--- a/students.xlsx
+++ b/students.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\cvruassignment_java\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEDF9D08-C88A-4A5D-A2B1-88C3F1295E57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DB3EAB2-E1DB-4F99-8991-DE6536E61495}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{46E0FFBC-8BE1-44BF-9A1A-4F987F2D7706}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{46E0FFBC-8BE1-44BF-9A1A-4F987F2D7706}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="409" uniqueCount="371">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="409" uniqueCount="370">
   <si>
     <t>ABHISHEK KUMAR</t>
   </si>
@@ -565,159 +565,30 @@
     <t>R25CA1CA0070</t>
   </si>
   <si>
-    <t>ABHISHEK  KUMAR</t>
-  </si>
-  <si>
     <t>ADITYA VARDHAN CHANDEL</t>
   </si>
   <si>
     <t>ADITYA KUMAR SAH</t>
   </si>
   <si>
-    <t>ARCHITA  ROY</t>
-  </si>
-  <si>
-    <t>ARYAN  RAJ</t>
-  </si>
-  <si>
-    <t>ASHISH  RAJ</t>
-  </si>
-  <si>
-    <t>AYUSH  KUMAR</t>
-  </si>
-  <si>
-    <t>BADAL  KUMAR</t>
-  </si>
-  <si>
     <t>CHAMAN KUMAR SINGH</t>
   </si>
   <si>
-    <t>DINANATH  KUMAR</t>
-  </si>
-  <si>
     <t>DIPANSHU KUMAR JHA</t>
   </si>
   <si>
-    <t>GAURAV  KUMAR</t>
-  </si>
-  <si>
-    <t>GOLU  KUMAR</t>
-  </si>
-  <si>
     <t>INDAL PRATAP SINGA</t>
   </si>
   <si>
     <t>KAMLESH KUMAR JHA</t>
   </si>
   <si>
-    <t>KANHAIYA  KUMAR</t>
-  </si>
-  <si>
-    <t>KOMAL  SHARMA</t>
-  </si>
-  <si>
-    <t>KUNAL  KUMAR</t>
-  </si>
-  <si>
-    <t>MD  IMTEYAJ</t>
-  </si>
-  <si>
-    <t>MD  WASIM</t>
-  </si>
-  <si>
-    <t>NIKHIL  KUMAR</t>
-  </si>
-  <si>
-    <t>NIKHIL  AANAND</t>
-  </si>
-  <si>
-    <t>NITIN  KUMAR</t>
-  </si>
-  <si>
-    <t>NURAISA  KHATUN</t>
-  </si>
-  <si>
-    <t>PALLAVI  KUMARI</t>
-  </si>
-  <si>
-    <t>PIYUSH  KUMAR</t>
-  </si>
-  <si>
-    <t>PRASHANT  KUMAR</t>
-  </si>
-  <si>
-    <t>PRATIK  RAJ</t>
-  </si>
-  <si>
-    <t>PRINCE  KUMAR</t>
-  </si>
-  <si>
-    <t>RAHUL  KUMAR</t>
-  </si>
-  <si>
-    <t>RAJA  KUMAR</t>
-  </si>
-  <si>
-    <t>RAJESH  KUMAR</t>
-  </si>
-  <si>
-    <t>RISHAV  KUMAR</t>
-  </si>
-  <si>
-    <t>SAHIL  KUMAR</t>
-  </si>
-  <si>
-    <t>SATYAM  KUMAR</t>
-  </si>
-  <si>
-    <t>SHALINI  KUMARI</t>
-  </si>
-  <si>
     <t>SHEKHAR KUMAR SINGH</t>
   </si>
   <si>
-    <t>SHIVAM  KUMAR</t>
-  </si>
-  <si>
     <t>SHIVRAJ KUMAR SINGH</t>
   </si>
   <si>
-    <t>SHUBHAM  KUMAR</t>
-  </si>
-  <si>
-    <t>SIMRAN  KUMARI</t>
-  </si>
-  <si>
-    <t>SUFIYAN  KHAN</t>
-  </si>
-  <si>
-    <t>SUMIT  KUMAR</t>
-  </si>
-  <si>
-    <t>SUSHANT  KUMAR</t>
-  </si>
-  <si>
-    <t>UJJAWAL  KUMAR</t>
-  </si>
-  <si>
-    <t>UNANTI  KUMARI</t>
-  </si>
-  <si>
-    <t>VICKY  KUMAR</t>
-  </si>
-  <si>
-    <t>VINIT  RAJ</t>
-  </si>
-  <si>
-    <t>VIPIN  KUMAR</t>
-  </si>
-  <si>
-    <t>VISHAL  KUMAR</t>
-  </si>
-  <si>
-    <t>MASUM  RAJ</t>
-  </si>
-  <si>
     <t>AZAD KUMAR</t>
   </si>
   <si>
@@ -880,129 +751,18 @@
     <t>L25ETDCS0009</t>
   </si>
   <si>
-    <t>RISHABH  RAJ</t>
-  </si>
-  <si>
-    <t>ADITI  BALA</t>
-  </si>
-  <si>
-    <t>ADITYA  KUMAR</t>
-  </si>
-  <si>
-    <t>ADITYA  RAJ</t>
-  </si>
-  <si>
-    <t>AKASH  KUMAR</t>
-  </si>
-  <si>
-    <t>ANAMICA  KUMARI</t>
-  </si>
-  <si>
-    <t>ANKITA  KUMARI</t>
-  </si>
-  <si>
-    <t>ANSH  RAJ</t>
-  </si>
-  <si>
-    <t>ARPANA  KUMARI</t>
-  </si>
-  <si>
-    <t>ARYAN  KUMAR</t>
-  </si>
-  <si>
-    <t>BABLU  KUMAR</t>
-  </si>
-  <si>
-    <t>DAYANAND  SAGAR</t>
-  </si>
-  <si>
-    <t>DEV  KUMAR</t>
-  </si>
-  <si>
-    <t>HIMANSHU  KUMAR</t>
-  </si>
-  <si>
-    <t>JUHI  KUMARI</t>
-  </si>
-  <si>
-    <t>KAJAL  KUMARI</t>
-  </si>
-  <si>
-    <t>KHUSHI  SINGH</t>
-  </si>
-  <si>
     <t>MANISH KUMAR MAHTO</t>
   </si>
   <si>
-    <t>MD  AFZAL</t>
-  </si>
-  <si>
-    <t>PALLAWI  SINGH</t>
-  </si>
-  <si>
-    <t>PARVATI  KUMARI</t>
-  </si>
-  <si>
-    <t>PRITI  PRIYA</t>
-  </si>
-  <si>
-    <t>PRIYANSHU  KUMAR</t>
-  </si>
-  <si>
-    <t>RAUSHAN  KUMAR</t>
-  </si>
-  <si>
-    <t>SANJEET  YADAV</t>
-  </si>
-  <si>
-    <t>SANU  KUMARI</t>
-  </si>
-  <si>
-    <t>SANYA  KUMARI</t>
-  </si>
-  <si>
-    <t>SATYAM  RAJ</t>
-  </si>
-  <si>
-    <t>SUDHANSHU  RAJ</t>
-  </si>
-  <si>
-    <t>UBAID  AHMED</t>
-  </si>
-  <si>
-    <t>UJJAVAL  KUMAR</t>
-  </si>
-  <si>
-    <t>VARSHA  KUMARI</t>
-  </si>
-  <si>
     <t>AMAN KUMAR SINGH</t>
   </si>
   <si>
     <t>AMARJEET KUMAR SINGH</t>
   </si>
   <si>
-    <t>AVINASH  KUMAR</t>
-  </si>
-  <si>
-    <t>MAHI  KUMARI</t>
-  </si>
-  <si>
     <t>MD MANIR ALAM</t>
   </si>
   <si>
-    <t>PRANAY  KUMAR</t>
-  </si>
-  <si>
-    <t>RISHINANDAN  KUMAR</t>
-  </si>
-  <si>
-    <t>ROHIT  KUMAR</t>
-  </si>
-  <si>
-    <t>SUBHAM  RAJ</t>
-  </si>
-  <si>
     <t>Differentiate between Java and C++ on the basis of platform dependency, memory management, pointers, and inheritance.</t>
   </si>
   <si>
@@ -1151,6 +911,243 @@
   </si>
   <si>
     <t>Find and correct the errors in an applet's paint() method when it is incorrectly declared and uses System.out.println() to display text.</t>
+  </si>
+  <si>
+    <t>ARCHITA ROY</t>
+  </si>
+  <si>
+    <t>ARYAN RAJ</t>
+  </si>
+  <si>
+    <t>ASHISH RAJ</t>
+  </si>
+  <si>
+    <t>AYUSH KUMAR</t>
+  </si>
+  <si>
+    <t>BADAL KUMAR</t>
+  </si>
+  <si>
+    <t>DINANATH KUMAR</t>
+  </si>
+  <si>
+    <t>GAURAV KUMAR</t>
+  </si>
+  <si>
+    <t>GOLU KUMAR</t>
+  </si>
+  <si>
+    <t>KANHAIYA KUMAR</t>
+  </si>
+  <si>
+    <t>KOMAL SHARMA</t>
+  </si>
+  <si>
+    <t>KUNAL KUMAR</t>
+  </si>
+  <si>
+    <t>MD IMTEYAJ</t>
+  </si>
+  <si>
+    <t>MD WASIM</t>
+  </si>
+  <si>
+    <t>NIKHIL KUMAR</t>
+  </si>
+  <si>
+    <t>NIKHIL AANAND</t>
+  </si>
+  <si>
+    <t>NITIN KUMAR</t>
+  </si>
+  <si>
+    <t>NURAISA KHATUN</t>
+  </si>
+  <si>
+    <t>PALLAVI KUMARI</t>
+  </si>
+  <si>
+    <t>PIYUSH KUMAR</t>
+  </si>
+  <si>
+    <t>PRASHANT KUMAR</t>
+  </si>
+  <si>
+    <t>PRATIK RAJ</t>
+  </si>
+  <si>
+    <t>PRINCE KUMAR</t>
+  </si>
+  <si>
+    <t>RAHUL KUMAR</t>
+  </si>
+  <si>
+    <t>RAJA KUMAR</t>
+  </si>
+  <si>
+    <t>RAJESH KUMAR</t>
+  </si>
+  <si>
+    <t>RISHAV KUMAR</t>
+  </si>
+  <si>
+    <t>SAHIL KUMAR</t>
+  </si>
+  <si>
+    <t>SATYAM KUMAR</t>
+  </si>
+  <si>
+    <t>SHALINI KUMARI</t>
+  </si>
+  <si>
+    <t>SHIVAM KUMAR</t>
+  </si>
+  <si>
+    <t>SHUBHAM KUMAR</t>
+  </si>
+  <si>
+    <t>SIMRAN KUMARI</t>
+  </si>
+  <si>
+    <t>SUFIYAN KHAN</t>
+  </si>
+  <si>
+    <t>SUMIT KUMAR</t>
+  </si>
+  <si>
+    <t>SUSHANT KUMAR</t>
+  </si>
+  <si>
+    <t>UJJAWAL KUMAR</t>
+  </si>
+  <si>
+    <t>UNANTI KUMARI</t>
+  </si>
+  <si>
+    <t>VICKY KUMAR</t>
+  </si>
+  <si>
+    <t>VINIT RAJ</t>
+  </si>
+  <si>
+    <t>VIPIN KUMAR</t>
+  </si>
+  <si>
+    <t>VISHAL KUMAR</t>
+  </si>
+  <si>
+    <t>MASUM RAJ</t>
+  </si>
+  <si>
+    <t>RISHABH RAJ</t>
+  </si>
+  <si>
+    <t>ADITI BALA</t>
+  </si>
+  <si>
+    <t>ADITYA KUMAR</t>
+  </si>
+  <si>
+    <t>ADITYA RAJ</t>
+  </si>
+  <si>
+    <t>AKASH KUMAR</t>
+  </si>
+  <si>
+    <t>ANAMICA KUMARI</t>
+  </si>
+  <si>
+    <t>ANKITA KUMARI</t>
+  </si>
+  <si>
+    <t>ANSH RAJ</t>
+  </si>
+  <si>
+    <t>ARPANA KUMARI</t>
+  </si>
+  <si>
+    <t>ARYAN KUMAR</t>
+  </si>
+  <si>
+    <t>BABLU KUMAR</t>
+  </si>
+  <si>
+    <t>DAYANAND SAGAR</t>
+  </si>
+  <si>
+    <t>DEV KUMAR</t>
+  </si>
+  <si>
+    <t>HIMANSHU KUMAR</t>
+  </si>
+  <si>
+    <t>JUHI KUMARI</t>
+  </si>
+  <si>
+    <t>KAJAL KUMARI</t>
+  </si>
+  <si>
+    <t>KHUSHI SINGH</t>
+  </si>
+  <si>
+    <t>MD AFZAL</t>
+  </si>
+  <si>
+    <t>PALLAWI SINGH</t>
+  </si>
+  <si>
+    <t>PARVATI KUMARI</t>
+  </si>
+  <si>
+    <t>PRITI PRIYA</t>
+  </si>
+  <si>
+    <t>PRIYANSHU KUMAR</t>
+  </si>
+  <si>
+    <t>RAUSHAN KUMAR</t>
+  </si>
+  <si>
+    <t>SANJEET YADAV</t>
+  </si>
+  <si>
+    <t>SANU KUMARI</t>
+  </si>
+  <si>
+    <t>SANYA KUMARI</t>
+  </si>
+  <si>
+    <t>SATYAM RAJ</t>
+  </si>
+  <si>
+    <t>SUDHANSHU RAJ</t>
+  </si>
+  <si>
+    <t>UBAID AHMED</t>
+  </si>
+  <si>
+    <t>UJJAVAL KUMAR</t>
+  </si>
+  <si>
+    <t>VARSHA KUMARI</t>
+  </si>
+  <si>
+    <t>AVINASH KUMAR</t>
+  </si>
+  <si>
+    <t>MAHI KUMARI</t>
+  </si>
+  <si>
+    <t>PRANAY KUMAR</t>
+  </si>
+  <si>
+    <t>RISHINANDAN KUMAR</t>
+  </si>
+  <si>
+    <t>ROHIT KUMAR</t>
+  </si>
+  <si>
+    <t>SUBHAM RAJ</t>
   </si>
 </sst>
 </file>
@@ -1660,7 +1657,7 @@
         <v>3</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>227</v>
+        <v>184</v>
       </c>
       <c r="D4" s="10" t="s">
         <v>107</v>
@@ -1674,7 +1671,7 @@
         <v>4</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D5" s="10" t="s">
         <v>108</v>
@@ -1688,7 +1685,7 @@
         <v>5</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D6" s="10" t="s">
         <v>109</v>
@@ -1702,7 +1699,7 @@
         <v>6</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>228</v>
+        <v>185</v>
       </c>
       <c r="D7" s="10" t="s">
         <v>110</v>
@@ -1716,7 +1713,7 @@
         <v>7</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>228</v>
+        <v>185</v>
       </c>
       <c r="D8" s="10" t="s">
         <v>111</v>
@@ -1730,7 +1727,7 @@
         <v>8</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>229</v>
+        <v>186</v>
       </c>
       <c r="D9" s="10" t="s">
         <v>112</v>
@@ -1744,7 +1741,7 @@
         <v>9</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>230</v>
+        <v>187</v>
       </c>
       <c r="D10" s="10" t="s">
         <v>113</v>
@@ -1786,7 +1783,7 @@
         <v>12</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>231</v>
+        <v>188</v>
       </c>
       <c r="D13" s="10" t="s">
         <v>116</v>
@@ -1800,7 +1797,7 @@
         <v>13</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>178</v>
+        <v>291</v>
       </c>
       <c r="D14" s="10" t="s">
         <v>117</v>
@@ -1814,7 +1811,7 @@
         <v>14</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>179</v>
+        <v>292</v>
       </c>
       <c r="D15" s="10" t="s">
         <v>118</v>
@@ -1828,7 +1825,7 @@
         <v>15</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>180</v>
+        <v>293</v>
       </c>
       <c r="D16" s="10" t="s">
         <v>119</v>
@@ -1842,7 +1839,7 @@
         <v>16</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>181</v>
+        <v>294</v>
       </c>
       <c r="D17" s="10" t="s">
         <v>120</v>
@@ -1856,7 +1853,7 @@
         <v>17</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>181</v>
+        <v>294</v>
       </c>
       <c r="D18" s="10" t="s">
         <v>121</v>
@@ -1870,7 +1867,7 @@
         <v>18</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>181</v>
+        <v>294</v>
       </c>
       <c r="D19" s="10" t="s">
         <v>122</v>
@@ -1884,7 +1881,7 @@
         <v>19</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>226</v>
+        <v>183</v>
       </c>
       <c r="D20" s="10" t="s">
         <v>123</v>
@@ -1898,7 +1895,7 @@
         <v>20</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>182</v>
+        <v>295</v>
       </c>
       <c r="D21" s="10" t="s">
         <v>124</v>
@@ -1912,7 +1909,7 @@
         <v>21</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="D22" s="10" t="s">
         <v>125</v>
@@ -1926,7 +1923,7 @@
         <v>22</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>184</v>
+        <v>296</v>
       </c>
       <c r="D23" s="10" t="s">
         <v>126</v>
@@ -1940,7 +1937,7 @@
         <v>23</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="D24" s="10" t="s">
         <v>127</v>
@@ -1954,7 +1951,7 @@
         <v>24</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>186</v>
+        <v>297</v>
       </c>
       <c r="D25" s="10" t="s">
         <v>128</v>
@@ -1968,7 +1965,7 @@
         <v>25</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>187</v>
+        <v>298</v>
       </c>
       <c r="D26" s="10" t="s">
         <v>129</v>
@@ -1982,7 +1979,7 @@
         <v>26</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>187</v>
+        <v>298</v>
       </c>
       <c r="D27" s="10" t="s">
         <v>130</v>
@@ -1996,7 +1993,7 @@
         <v>27</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>188</v>
+        <v>179</v>
       </c>
       <c r="D28" s="10" t="s">
         <v>131</v>
@@ -2010,7 +2007,7 @@
         <v>28</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>189</v>
+        <v>180</v>
       </c>
       <c r="D29" s="10" t="s">
         <v>132</v>
@@ -2024,7 +2021,7 @@
         <v>29</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>190</v>
+        <v>299</v>
       </c>
       <c r="D30" s="10" t="s">
         <v>133</v>
@@ -2038,7 +2035,7 @@
         <v>30</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>191</v>
+        <v>300</v>
       </c>
       <c r="D31" s="10" t="s">
         <v>134</v>
@@ -2052,7 +2049,7 @@
         <v>31</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>192</v>
+        <v>301</v>
       </c>
       <c r="D32" s="10" t="s">
         <v>135</v>
@@ -2066,7 +2063,7 @@
         <v>32</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>193</v>
+        <v>302</v>
       </c>
       <c r="D33" s="10" t="s">
         <v>136</v>
@@ -2080,7 +2077,7 @@
         <v>33</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>194</v>
+        <v>303</v>
       </c>
       <c r="D34" s="10" t="s">
         <v>137</v>
@@ -2094,7 +2091,7 @@
         <v>34</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>195</v>
+        <v>304</v>
       </c>
       <c r="D35" s="10" t="s">
         <v>138</v>
@@ -2108,7 +2105,7 @@
         <v>35</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>196</v>
+        <v>305</v>
       </c>
       <c r="D36" s="10" t="s">
         <v>139</v>
@@ -2122,7 +2119,7 @@
         <v>36</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>195</v>
+        <v>304</v>
       </c>
       <c r="D37" s="10" t="s">
         <v>140</v>
@@ -2136,7 +2133,7 @@
         <v>37</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>195</v>
+        <v>304</v>
       </c>
       <c r="D38" s="10" t="s">
         <v>141</v>
@@ -2150,7 +2147,7 @@
         <v>38</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>197</v>
+        <v>306</v>
       </c>
       <c r="D39" s="10" t="s">
         <v>142</v>
@@ -2164,7 +2161,7 @@
         <v>39</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>198</v>
+        <v>307</v>
       </c>
       <c r="D40" s="10" t="s">
         <v>143</v>
@@ -2178,7 +2175,7 @@
         <v>40</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>199</v>
+        <v>308</v>
       </c>
       <c r="D41" s="10" t="s">
         <v>144</v>
@@ -2192,7 +2189,7 @@
         <v>41</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>200</v>
+        <v>309</v>
       </c>
       <c r="D42" s="10" t="s">
         <v>145</v>
@@ -2206,7 +2203,7 @@
         <v>42</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>201</v>
+        <v>310</v>
       </c>
       <c r="D43" s="10" t="s">
         <v>146</v>
@@ -2220,7 +2217,7 @@
         <v>43</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>201</v>
+        <v>310</v>
       </c>
       <c r="D44" s="10" t="s">
         <v>147</v>
@@ -2234,7 +2231,7 @@
         <v>44</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>202</v>
+        <v>311</v>
       </c>
       <c r="D45" s="10" t="s">
         <v>148</v>
@@ -2248,7 +2245,7 @@
         <v>45</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>203</v>
+        <v>312</v>
       </c>
       <c r="D46" s="10" t="s">
         <v>149</v>
@@ -2262,7 +2259,7 @@
         <v>46</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>204</v>
+        <v>313</v>
       </c>
       <c r="D47" s="10" t="s">
         <v>150</v>
@@ -2276,7 +2273,7 @@
         <v>47</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>205</v>
+        <v>314</v>
       </c>
       <c r="D48" s="10" t="s">
         <v>151</v>
@@ -2290,7 +2287,7 @@
         <v>48</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>206</v>
+        <v>315</v>
       </c>
       <c r="D49" s="10" t="s">
         <v>152</v>
@@ -2304,7 +2301,7 @@
         <v>49</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>207</v>
+        <v>316</v>
       </c>
       <c r="D50" s="10" t="s">
         <v>153</v>
@@ -2318,7 +2315,7 @@
         <v>50</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>208</v>
+        <v>317</v>
       </c>
       <c r="D51" s="10" t="s">
         <v>154</v>
@@ -2332,7 +2329,7 @@
         <v>51</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>208</v>
+        <v>317</v>
       </c>
       <c r="D52" s="10" t="s">
         <v>155</v>
@@ -2346,7 +2343,7 @@
         <v>52</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>208</v>
+        <v>317</v>
       </c>
       <c r="D53" s="10" t="s">
         <v>156</v>
@@ -2360,7 +2357,7 @@
         <v>53</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>209</v>
+        <v>318</v>
       </c>
       <c r="D54" s="10" t="s">
         <v>157</v>
@@ -2374,7 +2371,7 @@
         <v>54</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>210</v>
+        <v>319</v>
       </c>
       <c r="D55" s="10" t="s">
         <v>158</v>
@@ -2388,7 +2385,7 @@
         <v>55</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>211</v>
+        <v>181</v>
       </c>
       <c r="D56" s="10" t="s">
         <v>159</v>
@@ -2402,7 +2399,7 @@
         <v>56</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>212</v>
+        <v>320</v>
       </c>
       <c r="D57" s="10" t="s">
         <v>160</v>
@@ -2416,7 +2413,7 @@
         <v>57</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>213</v>
+        <v>182</v>
       </c>
       <c r="D58" s="10" t="s">
         <v>161</v>
@@ -2430,7 +2427,7 @@
         <v>58</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>214</v>
+        <v>321</v>
       </c>
       <c r="D59" s="10" t="s">
         <v>162</v>
@@ -2444,7 +2441,7 @@
         <v>59</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>215</v>
+        <v>322</v>
       </c>
       <c r="D60" s="10" t="s">
         <v>163</v>
@@ -2458,7 +2455,7 @@
         <v>60</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>216</v>
+        <v>323</v>
       </c>
       <c r="D61" s="10" t="s">
         <v>164</v>
@@ -2472,7 +2469,7 @@
         <v>61</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>217</v>
+        <v>324</v>
       </c>
       <c r="D62" s="10" t="s">
         <v>165</v>
@@ -2486,7 +2483,7 @@
         <v>62</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>217</v>
+        <v>324</v>
       </c>
       <c r="D63" s="10" t="s">
         <v>166</v>
@@ -2500,7 +2497,7 @@
         <v>63</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>218</v>
+        <v>325</v>
       </c>
       <c r="D64" s="10" t="s">
         <v>167</v>
@@ -2514,7 +2511,7 @@
         <v>64</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>219</v>
+        <v>326</v>
       </c>
       <c r="D65" s="10" t="s">
         <v>168</v>
@@ -2528,7 +2525,7 @@
         <v>65</v>
       </c>
       <c r="C66" s="4" t="s">
-        <v>220</v>
+        <v>327</v>
       </c>
       <c r="D66" s="10" t="s">
         <v>169</v>
@@ -2542,7 +2539,7 @@
         <v>66</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>221</v>
+        <v>328</v>
       </c>
       <c r="D67" s="10" t="s">
         <v>170</v>
@@ -2556,7 +2553,7 @@
         <v>67</v>
       </c>
       <c r="C68" s="4" t="s">
-        <v>222</v>
+        <v>329</v>
       </c>
       <c r="D68" s="10" t="s">
         <v>171</v>
@@ -2570,7 +2567,7 @@
         <v>68</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>223</v>
+        <v>330</v>
       </c>
       <c r="D69" s="10" t="s">
         <v>172</v>
@@ -2584,7 +2581,7 @@
         <v>69</v>
       </c>
       <c r="C70" s="4" t="s">
-        <v>224</v>
+        <v>331</v>
       </c>
       <c r="D70" s="10" t="s">
         <v>173</v>
@@ -2598,7 +2595,7 @@
         <v>70</v>
       </c>
       <c r="C71" s="4" t="s">
-        <v>225</v>
+        <v>332</v>
       </c>
       <c r="D71" s="10" t="s">
         <v>174</v>
@@ -2612,10 +2609,10 @@
         <v>71</v>
       </c>
       <c r="C72" s="5" t="s">
-        <v>280</v>
+        <v>333</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>232</v>
+        <v>189</v>
       </c>
       <c r="E72" s="10" t="s">
         <v>77</v>
@@ -2626,10 +2623,10 @@
         <v>72</v>
       </c>
       <c r="C73" s="5" t="s">
-        <v>175</v>
+        <v>0</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>233</v>
+        <v>190</v>
       </c>
       <c r="E73" s="10" t="s">
         <v>78</v>
@@ -2640,10 +2637,10 @@
         <v>73</v>
       </c>
       <c r="C74" s="5" t="s">
-        <v>175</v>
+        <v>0</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>234</v>
+        <v>191</v>
       </c>
       <c r="E74" s="10" t="s">
         <v>79</v>
@@ -2654,10 +2651,10 @@
         <v>74</v>
       </c>
       <c r="C75" s="5" t="s">
-        <v>281</v>
+        <v>334</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>235</v>
+        <v>192</v>
       </c>
       <c r="E75" s="10" t="s">
         <v>80</v>
@@ -2668,10 +2665,10 @@
         <v>75</v>
       </c>
       <c r="C76" s="5" t="s">
-        <v>282</v>
+        <v>335</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>236</v>
+        <v>193</v>
       </c>
       <c r="E76" s="10" t="s">
         <v>81</v>
@@ -2682,10 +2679,10 @@
         <v>76</v>
       </c>
       <c r="C77" s="5" t="s">
-        <v>283</v>
+        <v>336</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>237</v>
+        <v>194</v>
       </c>
       <c r="E77" s="10" t="s">
         <v>82</v>
@@ -2696,10 +2693,10 @@
         <v>77</v>
       </c>
       <c r="C78" s="5" t="s">
-        <v>284</v>
+        <v>337</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>238</v>
+        <v>195</v>
       </c>
       <c r="E78" s="10" t="s">
         <v>83</v>
@@ -2710,10 +2707,10 @@
         <v>78</v>
       </c>
       <c r="C79" s="5" t="s">
-        <v>285</v>
+        <v>338</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>239</v>
+        <v>196</v>
       </c>
       <c r="E79" s="10" t="s">
         <v>84</v>
@@ -2724,10 +2721,10 @@
         <v>79</v>
       </c>
       <c r="C80" s="5" t="s">
-        <v>286</v>
+        <v>339</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>240</v>
+        <v>197</v>
       </c>
       <c r="E80" s="10" t="s">
         <v>85</v>
@@ -2738,10 +2735,10 @@
         <v>80</v>
       </c>
       <c r="C81" s="5" t="s">
-        <v>287</v>
+        <v>340</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>241</v>
+        <v>198</v>
       </c>
       <c r="E81" s="10" t="s">
         <v>86</v>
@@ -2752,10 +2749,10 @@
         <v>81</v>
       </c>
       <c r="C82" s="5" t="s">
-        <v>288</v>
+        <v>341</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>242</v>
+        <v>199</v>
       </c>
       <c r="E82" s="10" t="s">
         <v>87</v>
@@ -2766,10 +2763,10 @@
         <v>82</v>
       </c>
       <c r="C83" s="5" t="s">
-        <v>289</v>
+        <v>342</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>243</v>
+        <v>200</v>
       </c>
       <c r="E83" s="10" t="s">
         <v>88</v>
@@ -2780,10 +2777,10 @@
         <v>83</v>
       </c>
       <c r="C84" s="5" t="s">
-        <v>179</v>
+        <v>292</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>244</v>
+        <v>201</v>
       </c>
       <c r="E84" s="10" t="s">
         <v>89</v>
@@ -2794,10 +2791,10 @@
         <v>84</v>
       </c>
       <c r="C85" s="5" t="s">
-        <v>179</v>
+        <v>292</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>245</v>
+        <v>202</v>
       </c>
       <c r="E85" s="10" t="s">
         <v>90</v>
@@ -2808,10 +2805,10 @@
         <v>85</v>
       </c>
       <c r="C86" s="5" t="s">
-        <v>290</v>
+        <v>343</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>246</v>
+        <v>203</v>
       </c>
       <c r="E86" s="10" t="s">
         <v>91</v>
@@ -2822,10 +2819,10 @@
         <v>86</v>
       </c>
       <c r="C87" s="5" t="s">
-        <v>291</v>
+        <v>344</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>247</v>
+        <v>204</v>
       </c>
       <c r="E87" s="10" t="s">
         <v>92</v>
@@ -2836,10 +2833,10 @@
         <v>87</v>
       </c>
       <c r="C88" s="5" t="s">
-        <v>292</v>
+        <v>345</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>248</v>
+        <v>205</v>
       </c>
       <c r="E88" s="10" t="s">
         <v>93</v>
@@ -2850,10 +2847,10 @@
         <v>88</v>
       </c>
       <c r="C89" s="5" t="s">
-        <v>293</v>
+        <v>346</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>249</v>
+        <v>206</v>
       </c>
       <c r="E89" s="10" t="s">
         <v>94</v>
@@ -2864,10 +2861,10 @@
         <v>89</v>
       </c>
       <c r="C90" s="5" t="s">
-        <v>294</v>
+        <v>347</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>250</v>
+        <v>207</v>
       </c>
       <c r="E90" s="10" t="s">
         <v>95</v>
@@ -2878,10 +2875,10 @@
         <v>90</v>
       </c>
       <c r="C91" s="5" t="s">
-        <v>295</v>
+        <v>348</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>251</v>
+        <v>208</v>
       </c>
       <c r="E91" s="10" t="s">
         <v>96</v>
@@ -2892,10 +2889,10 @@
         <v>91</v>
       </c>
       <c r="C92" s="5" t="s">
-        <v>296</v>
+        <v>349</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>252</v>
+        <v>209</v>
       </c>
       <c r="E92" s="10" t="s">
         <v>97</v>
@@ -2906,10 +2903,10 @@
         <v>92</v>
       </c>
       <c r="C93" s="5" t="s">
-        <v>297</v>
+        <v>237</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>253</v>
+        <v>210</v>
       </c>
       <c r="E93" s="10" t="s">
         <v>98</v>
@@ -2920,10 +2917,10 @@
         <v>93</v>
       </c>
       <c r="C94" s="5" t="s">
-        <v>225</v>
+        <v>332</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>254</v>
+        <v>211</v>
       </c>
       <c r="E94" s="10" t="s">
         <v>99</v>
@@ -2934,10 +2931,10 @@
         <v>94</v>
       </c>
       <c r="C95" s="5" t="s">
-        <v>298</v>
+        <v>350</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>255</v>
+        <v>212</v>
       </c>
       <c r="E95" s="10" t="s">
         <v>100</v>
@@ -2948,10 +2945,10 @@
         <v>95</v>
       </c>
       <c r="C96" s="5" t="s">
-        <v>299</v>
+        <v>351</v>
       </c>
       <c r="D96" s="3" t="s">
-        <v>256</v>
+        <v>213</v>
       </c>
       <c r="E96" s="10" t="s">
         <v>101</v>
@@ -2962,10 +2959,10 @@
         <v>96</v>
       </c>
       <c r="C97" s="5" t="s">
-        <v>300</v>
+        <v>352</v>
       </c>
       <c r="D97" s="3" t="s">
-        <v>257</v>
+        <v>214</v>
       </c>
       <c r="E97" s="10" t="s">
         <v>102</v>
@@ -2976,10 +2973,10 @@
         <v>97</v>
       </c>
       <c r="C98" s="5" t="s">
-        <v>301</v>
+        <v>353</v>
       </c>
       <c r="D98" s="3" t="s">
-        <v>258</v>
+        <v>215</v>
       </c>
       <c r="E98" s="10" t="s">
         <v>103</v>
@@ -2990,10 +2987,10 @@
         <v>98</v>
       </c>
       <c r="C99" s="5" t="s">
-        <v>302</v>
+        <v>354</v>
       </c>
       <c r="D99" s="3" t="s">
-        <v>259</v>
+        <v>216</v>
       </c>
       <c r="E99" s="10" t="s">
         <v>104</v>
@@ -3004,10 +3001,10 @@
         <v>99</v>
       </c>
       <c r="C100" s="5" t="s">
-        <v>204</v>
+        <v>313</v>
       </c>
       <c r="D100" s="3" t="s">
-        <v>260</v>
+        <v>217</v>
       </c>
       <c r="E100" s="10" t="s">
         <v>102</v>
@@ -3018,10 +3015,10 @@
         <v>100</v>
       </c>
       <c r="C101" s="5" t="s">
-        <v>303</v>
+        <v>355</v>
       </c>
       <c r="D101" s="3" t="s">
-        <v>261</v>
+        <v>218</v>
       </c>
       <c r="E101" s="10" t="s">
         <v>7</v>
@@ -3032,10 +3029,10 @@
         <v>101</v>
       </c>
       <c r="C102" s="5" t="s">
-        <v>304</v>
+        <v>356</v>
       </c>
       <c r="D102" s="3" t="s">
-        <v>262</v>
+        <v>219</v>
       </c>
       <c r="E102" s="10" t="s">
         <v>8</v>
@@ -3046,10 +3043,10 @@
         <v>102</v>
       </c>
       <c r="C103" s="5" t="s">
-        <v>305</v>
+        <v>357</v>
       </c>
       <c r="D103" s="3" t="s">
-        <v>263</v>
+        <v>220</v>
       </c>
       <c r="E103" s="10" t="s">
         <v>9</v>
@@ -3060,10 +3057,10 @@
         <v>103</v>
       </c>
       <c r="C104" s="5" t="s">
-        <v>306</v>
+        <v>358</v>
       </c>
       <c r="D104" s="3" t="s">
-        <v>264</v>
+        <v>221</v>
       </c>
       <c r="E104" s="10" t="s">
         <v>10</v>
@@ -3074,10 +3071,10 @@
         <v>104</v>
       </c>
       <c r="C105" s="5" t="s">
-        <v>307</v>
+        <v>359</v>
       </c>
       <c r="D105" s="3" t="s">
-        <v>265</v>
+        <v>222</v>
       </c>
       <c r="E105" s="10" t="s">
         <v>11</v>
@@ -3088,10 +3085,10 @@
         <v>105</v>
       </c>
       <c r="C106" s="5" t="s">
-        <v>308</v>
+        <v>360</v>
       </c>
       <c r="D106" s="3" t="s">
-        <v>266</v>
+        <v>223</v>
       </c>
       <c r="E106" s="10" t="s">
         <v>12</v>
@@ -3102,10 +3099,10 @@
         <v>106</v>
       </c>
       <c r="C107" s="5" t="s">
-        <v>309</v>
+        <v>361</v>
       </c>
       <c r="D107" s="3" t="s">
-        <v>267</v>
+        <v>224</v>
       </c>
       <c r="E107" s="10" t="s">
         <v>13</v>
@@ -3116,10 +3113,10 @@
         <v>107</v>
       </c>
       <c r="C108" s="5" t="s">
-        <v>310</v>
+        <v>362</v>
       </c>
       <c r="D108" s="3" t="s">
-        <v>268</v>
+        <v>225</v>
       </c>
       <c r="E108" s="10" t="s">
         <v>14</v>
@@ -3130,10 +3127,10 @@
         <v>108</v>
       </c>
       <c r="C109" s="5" t="s">
-        <v>311</v>
+        <v>363</v>
       </c>
       <c r="D109" s="3" t="s">
-        <v>269</v>
+        <v>226</v>
       </c>
       <c r="E109" s="10" t="s">
         <v>15</v>
@@ -3144,10 +3141,10 @@
         <v>109</v>
       </c>
       <c r="C110" s="5" t="s">
-        <v>181</v>
+        <v>294</v>
       </c>
       <c r="D110" s="3" t="s">
-        <v>270</v>
+        <v>227</v>
       </c>
       <c r="E110" s="10" t="s">
         <v>16</v>
@@ -3158,10 +3155,10 @@
         <v>110</v>
       </c>
       <c r="C111" s="5" t="s">
-        <v>312</v>
+        <v>238</v>
       </c>
       <c r="D111" s="3" t="s">
-        <v>271</v>
+        <v>228</v>
       </c>
       <c r="E111" s="10" t="s">
         <v>17</v>
@@ -3172,10 +3169,10 @@
         <v>111</v>
       </c>
       <c r="C112" s="5" t="s">
-        <v>313</v>
+        <v>239</v>
       </c>
       <c r="D112" s="3" t="s">
-        <v>272</v>
+        <v>229</v>
       </c>
       <c r="E112" s="10" t="s">
         <v>18</v>
@@ -3186,10 +3183,10 @@
         <v>112</v>
       </c>
       <c r="C113" s="5" t="s">
-        <v>314</v>
+        <v>364</v>
       </c>
       <c r="D113" s="3" t="s">
-        <v>273</v>
+        <v>230</v>
       </c>
       <c r="E113" s="10" t="s">
         <v>19</v>
@@ -3200,10 +3197,10 @@
         <v>113</v>
       </c>
       <c r="C114" s="5" t="s">
-        <v>315</v>
+        <v>365</v>
       </c>
       <c r="D114" s="3" t="s">
-        <v>274</v>
+        <v>231</v>
       </c>
       <c r="E114" s="10" t="s">
         <v>67</v>
@@ -3214,10 +3211,10 @@
         <v>114</v>
       </c>
       <c r="C115" s="5" t="s">
-        <v>316</v>
+        <v>240</v>
       </c>
       <c r="D115" s="3" t="s">
-        <v>275</v>
+        <v>232</v>
       </c>
       <c r="E115" s="10" t="s">
         <v>68</v>
@@ -3228,10 +3225,10 @@
         <v>115</v>
       </c>
       <c r="C116" s="5" t="s">
-        <v>317</v>
+        <v>366</v>
       </c>
       <c r="D116" s="3" t="s">
-        <v>276</v>
+        <v>233</v>
       </c>
       <c r="E116" s="10" t="s">
         <v>69</v>
@@ -3242,10 +3239,10 @@
         <v>116</v>
       </c>
       <c r="C117" s="5" t="s">
-        <v>318</v>
+        <v>367</v>
       </c>
       <c r="D117" s="3" t="s">
-        <v>277</v>
+        <v>234</v>
       </c>
       <c r="E117" s="10" t="s">
         <v>70</v>
@@ -3256,10 +3253,10 @@
         <v>117</v>
       </c>
       <c r="C118" s="5" t="s">
-        <v>319</v>
+        <v>368</v>
       </c>
       <c r="D118" s="3" t="s">
-        <v>278</v>
+        <v>235</v>
       </c>
       <c r="E118" s="10" t="s">
         <v>71</v>
@@ -3270,10 +3267,10 @@
         <v>118</v>
       </c>
       <c r="C119" s="5" t="s">
-        <v>320</v>
+        <v>369</v>
       </c>
       <c r="D119" s="3" t="s">
-        <v>279</v>
+        <v>236</v>
       </c>
       <c r="E119" s="10" t="s">
         <v>72</v>
@@ -3301,252 +3298,252 @@
     </row>
     <row r="2" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="11" t="s">
-        <v>321</v>
+        <v>241</v>
       </c>
     </row>
     <row r="3" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="11" t="s">
-        <v>322</v>
+        <v>242</v>
       </c>
     </row>
     <row r="4" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="11" t="s">
-        <v>323</v>
+        <v>243</v>
       </c>
     </row>
     <row r="5" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="11" t="s">
-        <v>324</v>
+        <v>244</v>
       </c>
     </row>
     <row r="6" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="11" t="s">
-        <v>325</v>
+        <v>245</v>
       </c>
     </row>
     <row r="7" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="11" t="s">
-        <v>326</v>
+        <v>246</v>
       </c>
     </row>
     <row r="8" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="11" t="s">
-        <v>327</v>
+        <v>247</v>
       </c>
     </row>
     <row r="9" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="11" t="s">
-        <v>328</v>
+        <v>248</v>
       </c>
     </row>
     <row r="10" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="11" t="s">
-        <v>329</v>
+        <v>249</v>
       </c>
     </row>
     <row r="11" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="11" t="s">
-        <v>330</v>
+        <v>250</v>
       </c>
     </row>
     <row r="12" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="11" t="s">
-        <v>331</v>
+        <v>251</v>
       </c>
     </row>
     <row r="13" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="11" t="s">
-        <v>332</v>
+        <v>252</v>
       </c>
     </row>
     <row r="14" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="11" t="s">
-        <v>333</v>
+        <v>253</v>
       </c>
     </row>
     <row r="15" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="11" t="s">
-        <v>334</v>
+        <v>254</v>
       </c>
     </row>
     <row r="16" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="11" t="s">
-        <v>335</v>
+        <v>255</v>
       </c>
     </row>
     <row r="17" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="11" t="s">
-        <v>336</v>
+        <v>256</v>
       </c>
     </row>
     <row r="18" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="11" t="s">
-        <v>337</v>
+        <v>257</v>
       </c>
     </row>
     <row r="19" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="11" t="s">
-        <v>338</v>
+        <v>258</v>
       </c>
     </row>
     <row r="20" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="11" t="s">
-        <v>339</v>
+        <v>259</v>
       </c>
     </row>
     <row r="21" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="11" t="s">
-        <v>340</v>
+        <v>260</v>
       </c>
     </row>
     <row r="22" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="11" t="s">
-        <v>341</v>
+        <v>261</v>
       </c>
     </row>
     <row r="23" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="11" t="s">
-        <v>342</v>
+        <v>262</v>
       </c>
     </row>
     <row r="24" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="11" t="s">
-        <v>343</v>
+        <v>263</v>
       </c>
     </row>
     <row r="25" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="11" t="s">
-        <v>344</v>
+        <v>264</v>
       </c>
     </row>
     <row r="26" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="11" t="s">
-        <v>345</v>
+        <v>265</v>
       </c>
     </row>
     <row r="27" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="11" t="s">
-        <v>346</v>
+        <v>266</v>
       </c>
     </row>
     <row r="28" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="11" t="s">
-        <v>347</v>
+        <v>267</v>
       </c>
     </row>
     <row r="29" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" s="11" t="s">
-        <v>348</v>
+        <v>268</v>
       </c>
     </row>
     <row r="30" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="11" t="s">
-        <v>349</v>
+        <v>269</v>
       </c>
     </row>
     <row r="31" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="11" t="s">
-        <v>350</v>
+        <v>270</v>
       </c>
     </row>
     <row r="32" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="11" t="s">
-        <v>351</v>
+        <v>271</v>
       </c>
     </row>
     <row r="33" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" s="11" t="s">
-        <v>352</v>
+        <v>272</v>
       </c>
     </row>
     <row r="34" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="11" t="s">
-        <v>353</v>
+        <v>273</v>
       </c>
     </row>
     <row r="35" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="11" t="s">
-        <v>354</v>
+        <v>274</v>
       </c>
     </row>
     <row r="36" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A36" s="11" t="s">
-        <v>355</v>
+        <v>275</v>
       </c>
     </row>
     <row r="37" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A37" s="11" t="s">
-        <v>356</v>
+        <v>276</v>
       </c>
     </row>
     <row r="38" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A38" s="11" t="s">
-        <v>357</v>
+        <v>277</v>
       </c>
     </row>
     <row r="39" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="11" t="s">
-        <v>358</v>
+        <v>278</v>
       </c>
     </row>
     <row r="40" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="11" t="s">
-        <v>359</v>
+        <v>279</v>
       </c>
     </row>
     <row r="41" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A41" s="11" t="s">
-        <v>360</v>
+        <v>280</v>
       </c>
     </row>
     <row r="42" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A42" s="11" t="s">
-        <v>361</v>
+        <v>281</v>
       </c>
     </row>
     <row r="43" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A43" s="11" t="s">
-        <v>362</v>
+        <v>282</v>
       </c>
     </row>
     <row r="44" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" s="11" t="s">
-        <v>363</v>
+        <v>283</v>
       </c>
     </row>
     <row r="45" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A45" s="11" t="s">
-        <v>364</v>
+        <v>284</v>
       </c>
     </row>
     <row r="46" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A46" s="11" t="s">
-        <v>365</v>
+        <v>285</v>
       </c>
     </row>
     <row r="47" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A47" s="11" t="s">
-        <v>366</v>
+        <v>286</v>
       </c>
     </row>
     <row r="48" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A48" s="11" t="s">
-        <v>367</v>
+        <v>287</v>
       </c>
     </row>
     <row r="49" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A49" s="11" t="s">
-        <v>368</v>
+        <v>288</v>
       </c>
     </row>
     <row r="50" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A50" s="11" t="s">
-        <v>369</v>
+        <v>289</v>
       </c>
     </row>
     <row r="51" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A51" s="11" t="s">
-        <v>370</v>
+        <v>290</v>
       </c>
     </row>
   </sheetData>

--- a/students.xlsx
+++ b/students.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\cvruassignment_java\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DB3EAB2-E1DB-4F99-8991-DE6536E61495}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FC8FA0A-12A0-490E-AD0A-385B67D131A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{46E0FFBC-8BE1-44BF-9A1A-4F987F2D7706}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="409" uniqueCount="370">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="409" uniqueCount="390">
   <si>
     <t>ABHISHEK KUMAR</t>
   </si>
@@ -61,300 +61,6 @@
     <t>Questions</t>
   </si>
   <si>
-    <t>Q1, Q5, Q8, Q12, Q20, Q51, Q55, Q59, Q66, Q70</t>
-  </si>
-  <si>
-    <t>Q2, Q6, Q9, Q14, Q23, Q52, Q56, Q61, Q67, Q72</t>
-  </si>
-  <si>
-    <t>Q3, Q7, Q10, Q16, Q25, Q53, Q57, Q62, Q68, Q74</t>
-  </si>
-  <si>
-    <t>Q4, Q11, Q13, Q18, Q28, Q54, Q58, Q63, Q69, Q75</t>
-  </si>
-  <si>
-    <t>Q1, Q12, Q15, Q21, Q30, Q55, Q60, Q64, Q71, Q76</t>
-  </si>
-  <si>
-    <t>Q2, Q14, Q17, Q23, Q32, Q56, Q61, Q65, Q72, Q77</t>
-  </si>
-  <si>
-    <t>Q3, Q16, Q19, Q26, Q34, Q57, Q62, Q66, Q73, Q78</t>
-  </si>
-  <si>
-    <t>Q4, Q18, Q22, Q29, Q36, Q58, Q63, Q67, Q74, Q79</t>
-  </si>
-  <si>
-    <t>Q5, Q20, Q25, Q31, Q38, Q59, Q64, Q68, Q75, Q80</t>
-  </si>
-  <si>
-    <t>Q6, Q21, Q27, Q33, Q40, Q60, Q65, Q69, Q76, Q81</t>
-  </si>
-  <si>
-    <t>Q7, Q23, Q30, Q35, Q42, Q61, Q66, Q70, Q77, Q82</t>
-  </si>
-  <si>
-    <t>Q8, Q25, Q32, Q37, Q44, Q62, Q67, Q71, Q78, Q83</t>
-  </si>
-  <si>
-    <t>Q9, Q27, Q34, Q39, Q46, Q63, Q68, Q72, Q79, Q84</t>
-  </si>
-  <si>
-    <t>Q10, Q29, Q36, Q41, Q48, Q64, Q69, Q73, Q80, Q85</t>
-  </si>
-  <si>
-    <t>Q11, Q31, Q38, Q43, Q50, Q65, Q70, Q74, Q81, Q86</t>
-  </si>
-  <si>
-    <t>Q12, Q33, Q40, Q45, Q1, Q66, Q71, Q75, Q82, Q87</t>
-  </si>
-  <si>
-    <t>Q13, Q35, Q42, Q47, Q2, Q67, Q72, Q76, Q83, Q88</t>
-  </si>
-  <si>
-    <t>Q14, Q37, Q44, Q49, Q3, Q68, Q73, Q77, Q84, Q89</t>
-  </si>
-  <si>
-    <t>Q15, Q39, Q46, Q1, Q4, Q69, Q74, Q78, Q85, Q90</t>
-  </si>
-  <si>
-    <t>Q16, Q41, Q48, Q2, Q5, Q70, Q75, Q79, Q86, Q91</t>
-  </si>
-  <si>
-    <t>Q17, Q43, Q50, Q3, Q6, Q71, Q76, Q80, Q87, Q92</t>
-  </si>
-  <si>
-    <t>Q18, Q45, Q1, Q4, Q7, Q72, Q77, Q81, Q88, Q93</t>
-  </si>
-  <si>
-    <t>Q19, Q47, Q2, Q5, Q8, Q73, Q78, Q82, Q89, Q94</t>
-  </si>
-  <si>
-    <t>Q20, Q49, Q3, Q6, Q9, Q74, Q79, Q83, Q90, Q95</t>
-  </si>
-  <si>
-    <t>Q21, Q1, Q4, Q7, Q10, Q75, Q80, Q84, Q91, Q96</t>
-  </si>
-  <si>
-    <t>Q22, Q2, Q5, Q8, Q11, Q76, Q81, Q85, Q92, Q97</t>
-  </si>
-  <si>
-    <t>Q23, Q3, Q6, Q9, Q12, Q77, Q82, Q86, Q93, Q98</t>
-  </si>
-  <si>
-    <t>Q24, Q4, Q7, Q10, Q13, Q78, Q83, Q87, Q94, Q99</t>
-  </si>
-  <si>
-    <t>Q25, Q5, Q8, Q11, Q14, Q79, Q84, Q88, Q95, Q100</t>
-  </si>
-  <si>
-    <t>Q26, Q6, Q9, Q12, Q15, Q80, Q85, Q89, Q96, Q51</t>
-  </si>
-  <si>
-    <t>Q27, Q7, Q10, Q13, Q16, Q81, Q86, Q90, Q97, Q52</t>
-  </si>
-  <si>
-    <t>Q28, Q8, Q11, Q14, Q17, Q82, Q87, Q91, Q98, Q53</t>
-  </si>
-  <si>
-    <t>Q29, Q9, Q12, Q15, Q18, Q83, Q88, Q92, Q99, Q54</t>
-  </si>
-  <si>
-    <t>Q30, Q10, Q13, Q16, Q19, Q84, Q89, Q93, Q100, Q55</t>
-  </si>
-  <si>
-    <t>Q31, Q11, Q14, Q17, Q20, Q85, Q90, Q94, Q51, Q56</t>
-  </si>
-  <si>
-    <t>Q32, Q12, Q15, Q18, Q21, Q86, Q91, Q95, Q52, Q57</t>
-  </si>
-  <si>
-    <t>Q33, Q13, Q16, Q19, Q22, Q87, Q92, Q96, Q53, Q58</t>
-  </si>
-  <si>
-    <t>Q34, Q14, Q17, Q20, Q23, Q88, Q93, Q97, Q54, Q59</t>
-  </si>
-  <si>
-    <t>Q35, Q15, Q18, Q21, Q24, Q89, Q94, Q98, Q55, Q60</t>
-  </si>
-  <si>
-    <t>Q36, Q16, Q19, Q22, Q25, Q90, Q95, Q99, Q56, Q61</t>
-  </si>
-  <si>
-    <t>Q37, Q17, Q20, Q23, Q26, Q91, Q96, Q100, Q57, Q62</t>
-  </si>
-  <si>
-    <t>Q38, Q18, Q21, Q24, Q27, Q92, Q51, Q61, Q58, Q63</t>
-  </si>
-  <si>
-    <t>Q39, Q19, Q22, Q25, Q28, Q93, Q52, Q62, Q59, Q64</t>
-  </si>
-  <si>
-    <t>Q40, Q20, Q23, Q26, Q29, Q94, Q53, Q63, Q60, Q65</t>
-  </si>
-  <si>
-    <t>Q41, Q21, Q24, Q27, Q30, Q95, Q54, Q64, Q61, Q66</t>
-  </si>
-  <si>
-    <t>Q42, Q22, Q25, Q28, Q31, Q96, Q55, Q65, Q62, Q67</t>
-  </si>
-  <si>
-    <t>Q43, Q23, Q26, Q29, Q32, Q97, Q56, Q66, Q63, Q68</t>
-  </si>
-  <si>
-    <t>Q44, Q24, Q27, Q30, Q33, Q98, Q57, Q67, Q64, Q69</t>
-  </si>
-  <si>
-    <t>Q45, Q25, Q28, Q31, Q34, Q99, Q58, Q68, Q65, Q70</t>
-  </si>
-  <si>
-    <t>Q46, Q26, Q29, Q32, Q35, Q100, Q59, Q69, Q66, Q71</t>
-  </si>
-  <si>
-    <t>Q47, Q27, Q30, Q33, Q36, Q51, Q60, Q70, Q67, Q72</t>
-  </si>
-  <si>
-    <t>Q48, Q28, Q31, Q34, Q37, Q52, Q61, Q71, Q68, Q73</t>
-  </si>
-  <si>
-    <t>Q49, Q29, Q32, Q35, Q38, Q53, Q62, Q72, Q69, Q74</t>
-  </si>
-  <si>
-    <t>Q50, Q30, Q33, Q36, Q39, Q54, Q63, Q73, Q70, Q75</t>
-  </si>
-  <si>
-    <t>Q1, Q31, Q34, Q37, Q40, Q55, Q64, Q74, Q71, Q76</t>
-  </si>
-  <si>
-    <t>Q2, Q32, Q35, Q38, Q41, Q56, Q65, Q75, Q72, Q77</t>
-  </si>
-  <si>
-    <t>Q3, Q33, Q36, Q39, Q42, Q57, Q66, Q76, Q73, Q78</t>
-  </si>
-  <si>
-    <t>Q4, Q34, Q37, Q40, Q43, Q58, Q67, Q77, Q74, Q79</t>
-  </si>
-  <si>
-    <t>Q5, Q35, Q38, Q41, Q44, Q59, Q68, Q78, Q75, Q80</t>
-  </si>
-  <si>
-    <t>Q6, Q36, Q39, Q42, Q45, Q60, Q69, Q79, Q76, Q81</t>
-  </si>
-  <si>
-    <t>Q7, Q37, Q40, Q43, Q46, Q61, Q70, Q80, Q77, Q82</t>
-  </si>
-  <si>
-    <t>Q8, Q38, Q41, Q44, Q47, Q62, Q71, Q81, Q78, Q83</t>
-  </si>
-  <si>
-    <t>Q9, Q39, Q42, Q45, Q48, Q63, Q72, Q82, Q79, Q84</t>
-  </si>
-  <si>
-    <t>Q10, Q40, Q43, Q46, Q49, Q64, Q73, Q83, Q80, Q85</t>
-  </si>
-  <si>
-    <t>Q11, Q41, Q44, Q47, Q50, Q65, Q74, Q84, Q81, Q86</t>
-  </si>
-  <si>
-    <t>Q12, Q42, Q45, Q48, Q1, Q66, Q75, Q85, Q82, Q87</t>
-  </si>
-  <si>
-    <t>Q13, Q43, Q46, Q49, Q2, Q67, Q76, Q86, Q83, Q88</t>
-  </si>
-  <si>
-    <t>Q14, Q44, Q47, Q50, Q3, Q68, Q77, Q87, Q84, Q89</t>
-  </si>
-  <si>
-    <t>Q15, Q45, Q48, Q1, Q4, Q69, Q78, Q88, Q85, Q90</t>
-  </si>
-  <si>
-    <t>Q16, Q46, Q49, Q2, Q5, Q70, Q79, Q89, Q86, Q91</t>
-  </si>
-  <si>
-    <t>Q17, Q47, Q50, Q3, Q6, Q71, Q80, Q90, Q87, Q92</t>
-  </si>
-  <si>
-    <t>Q18, Q48, Q1, Q4, Q7, Q72, Q81, Q91, Q88, Q93</t>
-  </si>
-  <si>
-    <t>Q19, Q49, Q2, Q5, Q8, Q73, Q82, Q92, Q89, Q94</t>
-  </si>
-  <si>
-    <t>Q20, Q50, Q3, Q6, Q9, Q74, Q83, Q93, Q90, Q95</t>
-  </si>
-  <si>
-    <t>Q1, Q4, Q7, Q10, Q11, Q75, Q84, Q94, Q91, Q96</t>
-  </si>
-  <si>
-    <t>Q2, Q5, Q8, Q12, Q13, Q76, Q85, Q95, Q92, Q97</t>
-  </si>
-  <si>
-    <t>Q3, Q6, Q9, Q14, Q15, Q77, Q86, Q96, Q93, Q98</t>
-  </si>
-  <si>
-    <t>Q4, Q7, Q10, Q16, Q17, Q78, Q87, Q97, Q94, Q99</t>
-  </si>
-  <si>
-    <t>Q5, Q8, Q11, Q18, Q19, Q79, Q88, Q98, Q95, Q100</t>
-  </si>
-  <si>
-    <t>Q6, Q9, Q12, Q20, Q21, Q80, Q89, Q99, Q96, Q51</t>
-  </si>
-  <si>
-    <t>Q7, Q10, Q13, Q22, Q23, Q81, Q90, Q100, Q97, Q52</t>
-  </si>
-  <si>
-    <t>Q8, Q11, Q14, Q24, Q25, Q82, Q91, Q51, Q98, Q53</t>
-  </si>
-  <si>
-    <t>Q9, Q12, Q15, Q26, Q27, Q83, Q92, Q52, Q99, Q54</t>
-  </si>
-  <si>
-    <t>Q10, Q13, Q16, Q28, Q29, Q84, Q93, Q53, Q100, Q55</t>
-  </si>
-  <si>
-    <t>Q11, Q14, Q17, Q30, Q31, Q85, Q94, Q54, Q51, Q56</t>
-  </si>
-  <si>
-    <t>Q12, Q15, Q18, Q32, Q33, Q86, Q95, Q55, Q52, Q57</t>
-  </si>
-  <si>
-    <t>Q13, Q16, Q19, Q34, Q35, Q87, Q96, Q56, Q53, Q58</t>
-  </si>
-  <si>
-    <t>Q14, Q17, Q20, Q36, Q37, Q88, Q97, Q57, Q54, Q59</t>
-  </si>
-  <si>
-    <t>Q15, Q18, Q21, Q38, Q39, Q89, Q98, Q58, Q55, Q60</t>
-  </si>
-  <si>
-    <t>Q16, Q19, Q22, Q40, Q41, Q90, Q99, Q59, Q56, Q61</t>
-  </si>
-  <si>
-    <t>Q17, Q20, Q23, Q42, Q44, Q91, Q95, Q58, Q60, Q61</t>
-  </si>
-  <si>
-    <t>Q18, Q21, Q24, Q43, Q45, Q92, Q96, Q59, Q61, Q62</t>
-  </si>
-  <si>
-    <t>Q19, Q22, Q25, Q44, Q46, Q93, Q97, Q60, Q62, Q63</t>
-  </si>
-  <si>
-    <t>Q20, Q23, Q26, Q45, Q47, Q94, Q98, Q61, Q63, Q64</t>
-  </si>
-  <si>
-    <t>Q1, Q24, Q27, Q46, Q48, Q95, Q99, Q62, Q64, Q65</t>
-  </si>
-  <si>
-    <t>Q2, Q25, Q28, Q47, Q49, Q96, Q100, Q63, Q65, Q66</t>
-  </si>
-  <si>
-    <t>Q3, Q26, Q29, Q48, Q50, Q97, Q51, Q64, Q66, Q67</t>
-  </si>
-  <si>
-    <t>Q3, Q26, Q29, Q48, Q50, Q97, Q51, Q64, Q66, Q68</t>
-  </si>
-  <si>
     <t>R25CA1CA0001</t>
   </si>
   <si>
@@ -1148,13 +854,367 @@
   </si>
   <si>
     <t>SUBHAM RAJ</t>
+  </si>
+  <si>
+    <t>Q35, Q29, Q15, Q41, Q23, Q30, Q19, Q12, Q45, Q28</t>
+  </si>
+  <si>
+    <t>Q6, Q18, Q45, Q17, Q10, Q28, Q43, Q15, Q33, Q9</t>
+  </si>
+  <si>
+    <t>Q17, Q24, Q38, Q7, Q16, Q6, Q21, Q41, Q18, Q13</t>
+  </si>
+  <si>
+    <t>Q29, Q26, Q13, Q48, Q34, Q33, Q8, Q7, Q12, Q20</t>
+  </si>
+  <si>
+    <t>Q7, Q14, Q42, Q32, Q19, Q27, Q9, Q44, Q35, Q28</t>
+  </si>
+  <si>
+    <t>Q39, Q29, Q40, Q31, Q26, Q28, Q1, Q32, Q50, Q3</t>
+  </si>
+  <si>
+    <t>Q33, Q39, Q41, Q48, Q19, Q47, Q28, Q30, Q22, Q9</t>
+  </si>
+  <si>
+    <t>Q29, Q50, Q42, Q20, Q11, Q41, Q24, Q35, Q6, Q44</t>
+  </si>
+  <si>
+    <t>Q21, Q17, Q29, Q31, Q28, Q38, Q46, Q49, Q41, Q48</t>
+  </si>
+  <si>
+    <t>Q33, Q19, Q11, Q1, Q44, Q28, Q15, Q39, Q32, Q17</t>
+  </si>
+  <si>
+    <t>Q22, Q50, Q10, Q18, Q33, Q31, Q16, Q34, Q27, Q36</t>
+  </si>
+  <si>
+    <t>Q48, Q9, Q16, Q32, Q21, Q3, Q37, Q25, Q23, Q5</t>
+  </si>
+  <si>
+    <t>Q49, Q41, Q12, Q7, Q1, Q13, Q45, Q39, Q40, Q5</t>
+  </si>
+  <si>
+    <t>Q6, Q22, Q35, Q28, Q42, Q30, Q5, Q19, Q13, Q10</t>
+  </si>
+  <si>
+    <t>Q26, Q19, Q36, Q49, Q8, Q39, Q23, Q1, Q43, Q32</t>
+  </si>
+  <si>
+    <t>Q15, Q35, Q41, Q16, Q42, Q48, Q38, Q36, Q3, Q5</t>
+  </si>
+  <si>
+    <t>Q21, Q46, Q20, Q16, Q6, Q45, Q40, Q18, Q30, Q5</t>
+  </si>
+  <si>
+    <t>Q14, Q1, Q38, Q29, Q16, Q37, Q43, Q45, Q11, Q47</t>
+  </si>
+  <si>
+    <t>Q49, Q36, Q8, Q24, Q40, Q50, Q45, Q14, Q7, Q46</t>
+  </si>
+  <si>
+    <t>Q47, Q6, Q4, Q28, Q30, Q10, Q20, Q38, Q32, Q3</t>
+  </si>
+  <si>
+    <t>Q9, Q36, Q34, Q13, Q45, Q19, Q18, Q41, Q43, Q12</t>
+  </si>
+  <si>
+    <t>Q46, Q27, Q41, Q13, Q11, Q50, Q8, Q19, Q34, Q31</t>
+  </si>
+  <si>
+    <t>Q41, Q4, Q45, Q21, Q18, Q49, Q50, Q36, Q1, Q12</t>
+  </si>
+  <si>
+    <t>Q36, Q4, Q6, Q49, Q1, Q41, Q18, Q12, Q25, Q20</t>
+  </si>
+  <si>
+    <t>Q3, Q23, Q14, Q33, Q5, Q38, Q8, Q40, Q48, Q1</t>
+  </si>
+  <si>
+    <t>Q27, Q4, Q14, Q50, Q7, Q17, Q40, Q2, Q5, Q9</t>
+  </si>
+  <si>
+    <t>Q41, Q4, Q29, Q22, Q26, Q37, Q46, Q38, Q36, Q34</t>
+  </si>
+  <si>
+    <t>Q36, Q48, Q10, Q7, Q43, Q37, Q47, Q17, Q20, Q45</t>
+  </si>
+  <si>
+    <t>Q7, Q36, Q37, Q42, Q11, Q25, Q15, Q29, Q49, Q2</t>
+  </si>
+  <si>
+    <t>Q43, Q27, Q34, Q29, Q15, Q32, Q17, Q35, Q10, Q18</t>
+  </si>
+  <si>
+    <t>Q5, Q22, Q38, Q46, Q7, Q19, Q25, Q31, Q30, Q23</t>
+  </si>
+  <si>
+    <t>Q28, Q40, Q26, Q33, Q14, Q13, Q21, Q7, Q36, Q50</t>
+  </si>
+  <si>
+    <t>Q37, Q3, Q16, Q50, Q41, Q39, Q43, Q18, Q28, Q11</t>
+  </si>
+  <si>
+    <t>Q12, Q4, Q42, Q41, Q2, Q22, Q34, Q35, Q8, Q39</t>
+  </si>
+  <si>
+    <t>Q24, Q27, Q50, Q35, Q32, Q5, Q15, Q16, Q31, Q39</t>
+  </si>
+  <si>
+    <t>Q41, Q23, Q25, Q13, Q35, Q46, Q36, Q22, Q34, Q11</t>
+  </si>
+  <si>
+    <t>Q10, Q12, Q41, Q42, Q28, Q48, Q11, Q5, Q36, Q35</t>
+  </si>
+  <si>
+    <t>Q34, Q44, Q5, Q49, Q12, Q45, Q30, Q15, Q26, Q41</t>
+  </si>
+  <si>
+    <t>Q9, Q43, Q21, Q45, Q15, Q35, Q8, Q46, Q48, Q37</t>
+  </si>
+  <si>
+    <t>Q5, Q16, Q45, Q26, Q41, Q40, Q46, Q29, Q31, Q12</t>
+  </si>
+  <si>
+    <t>Q15, Q19, Q35, Q29, Q49, Q42, Q36, Q27, Q32, Q47</t>
+  </si>
+  <si>
+    <t>Q29, Q42, Q21, Q32, Q14, Q28, Q18, Q16, Q5, Q1</t>
+  </si>
+  <si>
+    <t>Q19, Q43, Q32, Q2, Q45, Q39, Q7, Q10, Q48, Q13</t>
+  </si>
+  <si>
+    <t>Q7, Q9, Q45, Q44, Q25, Q32, Q22, Q15, Q21, Q1</t>
+  </si>
+  <si>
+    <t>Q13, Q15, Q38, Q20, Q5, Q26, Q17, Q7, Q28, Q10</t>
+  </si>
+  <si>
+    <t>Q33, Q30, Q50, Q21, Q39, Q24, Q13, Q31, Q40, Q36</t>
+  </si>
+  <si>
+    <t>Q1, Q4, Q3, Q16, Q22, Q45, Q11, Q46, Q35, Q36</t>
+  </si>
+  <si>
+    <t>Q4, Q43, Q39, Q47, Q10, Q20, Q1, Q32, Q36, Q41</t>
+  </si>
+  <si>
+    <t>Q22, Q7, Q16, Q28, Q43, Q1, Q21, Q15, Q30, Q49</t>
+  </si>
+  <si>
+    <t>Q12, Q29, Q49, Q15, Q32, Q1, Q48, Q13, Q47, Q45</t>
+  </si>
+  <si>
+    <t>Q36, Q39, Q23, Q14, Q13, Q35, Q40, Q43, Q44, Q22</t>
+  </si>
+  <si>
+    <t>Q40, Q29, Q43, Q38, Q35, Q25, Q46, Q5, Q23, Q6</t>
+  </si>
+  <si>
+    <t>Q19, Q20, Q18, Q30, Q27, Q4, Q6, Q28, Q35, Q33</t>
+  </si>
+  <si>
+    <t>Q32, Q26, Q38, Q12, Q29, Q34, Q7, Q36, Q28, Q35</t>
+  </si>
+  <si>
+    <t>Q50, Q35, Q47, Q36, Q19, Q33, Q37, Q13, Q12, Q43</t>
+  </si>
+  <si>
+    <t>Q18, Q17, Q15, Q47, Q32, Q27, Q30, Q21, Q24, Q26</t>
+  </si>
+  <si>
+    <t>Q24, Q8, Q19, Q47, Q50, Q29, Q20, Q46, Q5, Q41</t>
+  </si>
+  <si>
+    <t>Q23, Q3, Q2, Q35, Q42, Q29, Q1, Q38, Q47, Q20</t>
+  </si>
+  <si>
+    <t>Q49, Q6, Q26, Q21, Q18, Q24, Q36, Q44, Q32, Q11</t>
+  </si>
+  <si>
+    <t>Q25, Q17, Q3, Q26, Q18, Q2, Q37, Q49, Q22, Q39</t>
+  </si>
+  <si>
+    <t>Q18, Q19, Q27, Q2, Q38, Q26, Q5, Q14, Q6, Q8</t>
+  </si>
+  <si>
+    <t>Q41, Q35, Q40, Q29, Q48, Q31, Q27, Q30, Q22, Q16</t>
+  </si>
+  <si>
+    <t>Q19, Q31, Q18, Q44, Q37, Q48, Q29, Q9, Q20, Q26</t>
+  </si>
+  <si>
+    <t>Q33, Q7, Q27, Q2, Q43, Q21, Q28, Q17, Q30, Q32</t>
+  </si>
+  <si>
+    <t>Q50, Q13, Q14, Q43, Q37, Q45, Q24, Q22, Q36, Q4</t>
+  </si>
+  <si>
+    <t>Q20, Q26, Q44, Q32, Q23, Q35, Q37, Q2, Q31, Q14</t>
+  </si>
+  <si>
+    <t>Q13, Q39, Q4, Q28, Q45, Q26, Q10, Q40, Q2, Q5</t>
+  </si>
+  <si>
+    <t>Q48, Q39, Q30, Q33, Q32, Q36, Q46, Q43, Q41, Q17</t>
+  </si>
+  <si>
+    <t>Q38, Q50, Q32, Q10, Q47, Q26, Q14, Q5, Q1, Q15</t>
+  </si>
+  <si>
+    <t>Q14, Q1, Q22, Q30, Q12, Q13, Q9, Q15, Q11, Q31</t>
+  </si>
+  <si>
+    <t>Q21, Q9, Q15, Q44, Q11, Q1, Q13, Q34, Q39, Q26</t>
+  </si>
+  <si>
+    <t>Q39, Q30, Q32, Q18, Q43, Q24, Q42, Q50, Q34, Q22</t>
+  </si>
+  <si>
+    <t>Q24, Q10, Q33, Q13, Q26, Q5, Q28, Q14, Q3, Q16</t>
+  </si>
+  <si>
+    <t>Q16, Q24, Q32, Q8, Q44, Q22, Q48, Q7, Q38, Q43</t>
+  </si>
+  <si>
+    <t>Q30, Q49, Q48, Q4, Q11, Q42, Q32, Q2, Q7, Q24</t>
+  </si>
+  <si>
+    <t>Q48, Q15, Q1, Q8, Q29, Q34, Q21, Q27, Q17, Q4</t>
+  </si>
+  <si>
+    <t>Q23, Q16, Q30, Q18, Q50, Q40, Q38, Q1, Q11, Q36</t>
+  </si>
+  <si>
+    <t>Q28, Q27, Q33, Q40, Q25, Q2, Q50, Q44, Q21, Q49</t>
+  </si>
+  <si>
+    <t>Q39, Q46, Q27, Q22, Q49, Q50, Q37, Q34, Q12, Q3</t>
+  </si>
+  <si>
+    <t>Q21, Q49, Q40, Q16, Q39, Q5, Q36, Q45, Q34, Q31</t>
+  </si>
+  <si>
+    <t>Q38, Q14, Q21, Q19, Q36, Q39, Q43, Q42, Q32, Q34</t>
+  </si>
+  <si>
+    <t>Q14, Q9, Q31, Q48, Q20, Q47, Q21, Q27, Q44, Q40</t>
+  </si>
+  <si>
+    <t>Q36, Q6, Q7, Q28, Q11, Q15, Q30, Q29, Q24, Q46</t>
+  </si>
+  <si>
+    <t>Q15, Q1, Q12, Q6, Q13, Q11, Q35, Q31, Q4, Q48</t>
+  </si>
+  <si>
+    <t>Q1, Q18, Q49, Q45, Q37, Q50, Q35, Q2, Q6, Q11</t>
+  </si>
+  <si>
+    <t>Q29, Q39, Q26, Q33, Q27, Q2, Q43, Q4, Q48, Q15</t>
+  </si>
+  <si>
+    <t>Q4, Q45, Q10, Q9, Q46, Q39, Q41, Q16, Q22, Q28</t>
+  </si>
+  <si>
+    <t>Q34, Q38, Q17, Q40, Q44, Q1, Q9, Q8, Q15, Q42</t>
+  </si>
+  <si>
+    <t>Q29, Q12, Q27, Q14, Q4, Q16, Q40, Q38, Q17, Q31</t>
+  </si>
+  <si>
+    <t>Q30, Q9, Q13, Q19, Q14, Q37, Q4, Q33, Q1, Q28</t>
+  </si>
+  <si>
+    <t>Q9, Q1, Q3, Q10, Q42, Q2, Q11, Q38, Q39, Q29</t>
+  </si>
+  <si>
+    <t>Q12, Q50, Q5, Q7, Q24, Q17, Q32, Q31, Q10, Q9</t>
+  </si>
+  <si>
+    <t>Q36, Q47, Q9, Q27, Q25, Q18, Q31, Q21, Q39, Q19</t>
+  </si>
+  <si>
+    <t>Q38, Q8, Q31, Q45, Q43, Q4, Q44, Q39, Q21, Q3</t>
+  </si>
+  <si>
+    <t>Q1, Q25, Q19, Q3, Q49, Q36, Q42, Q22, Q34, Q29</t>
+  </si>
+  <si>
+    <t>Q4, Q48, Q50, Q18, Q9, Q14, Q47, Q8, Q39, Q6</t>
+  </si>
+  <si>
+    <t>Q41, Q7, Q9, Q33, Q13, Q21, Q23, Q20, Q34, Q16</t>
+  </si>
+  <si>
+    <t>Q50, Q40, Q21, Q7, Q29, Q5, Q24, Q47, Q49, Q41</t>
+  </si>
+  <si>
+    <t>Q38, Q2, Q10, Q44, Q23, Q47, Q27, Q36, Q37, Q1</t>
+  </si>
+  <si>
+    <t>Q47, Q50, Q6, Q27, Q11, Q8, Q42, Q17, Q49, Q5</t>
+  </si>
+  <si>
+    <t>Q18, Q42, Q7, Q24, Q9, Q2, Q35, Q13, Q10, Q33</t>
+  </si>
+  <si>
+    <t>Q35, Q10, Q9, Q37, Q50, Q22, Q17, Q14, Q11, Q24</t>
+  </si>
+  <si>
+    <t>Q29, Q36, Q30, Q20, Q4, Q25, Q40, Q6, Q2, Q49</t>
+  </si>
+  <si>
+    <t>Q20, Q24, Q47, Q22, Q44, Q8, Q6, Q32, Q36, Q31</t>
+  </si>
+  <si>
+    <t>Q38, Q16, Q21, Q18, Q31, Q32, Q24, Q3, Q45, Q20</t>
+  </si>
+  <si>
+    <t>Q44, Q12, Q16, Q11, Q42, Q20, Q31, Q19, Q35, Q15</t>
+  </si>
+  <si>
+    <t>Q6, Q30, Q21, Q9, Q48, Q25, Q8, Q15, Q2, Q47</t>
+  </si>
+  <si>
+    <t>Q9, Q17, Q44, Q1, Q26, Q33, Q28, Q20, Q48, Q43</t>
+  </si>
+  <si>
+    <t>Q3, Q5, Q11, Q2, Q34, Q1, Q27, Q6, Q12, Q44</t>
+  </si>
+  <si>
+    <t>Q22, Q34, Q35, Q8, Q48, Q11, Q20, Q15, Q42, Q25</t>
+  </si>
+  <si>
+    <t>Q5, Q15, Q31, Q40, Q27, Q11, Q34, Q25, Q38, Q47</t>
+  </si>
+  <si>
+    <t>Q3, Q29, Q17, Q20, Q10, Q1, Q6, Q33, Q8, Q4</t>
+  </si>
+  <si>
+    <t>Q23, Q50, Q33, Q26, Q39, Q43, Q32, Q7, Q34, Q25</t>
+  </si>
+  <si>
+    <t>Q33, Q3, Q17, Q34, Q16, Q9, Q11, Q48, Q30, Q35</t>
+  </si>
+  <si>
+    <t>Q3, Q9, Q34, Q8, Q10, Q48, Q37, Q29, Q26, Q42</t>
+  </si>
+  <si>
+    <t>Q29, Q6, Q34, Q36, Q43, Q30, Q35, Q11, Q23, Q17</t>
+  </si>
+  <si>
+    <t>Q4, Q18, Q21, Q9, Q35, Q34, Q16, Q29, Q13, Q33</t>
+  </si>
+  <si>
+    <t>Q42, Q18, Q28, Q50, Q44, Q32, Q29, Q24, Q22, Q5</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1181,6 +1241,11 @@
       <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Carlito"/>
     </font>
   </fonts>
   <fills count="3">
@@ -1252,7 +1317,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -1283,6 +1348,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1600,17 +1668,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{98158040-D413-493D-8C9B-BBE0F4269401}">
   <dimension ref="B1:E119"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="6.28515625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="18.42578125" style="6" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="15.7109375" customWidth="1"/>
-    <col min="5" max="5" width="46.5703125" customWidth="1"/>
+    <col min="5" max="5" width="52.7109375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="115.42578125" customWidth="1"/>
     <col min="7" max="31" width="7.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:5" ht="15.75" thickBot="1">
       <c r="B1" s="7" t="s">
         <v>2</v>
       </c>
@@ -1624,7 +1692,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="2:5" s="2" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:5" s="2" customFormat="1" ht="20.25" customHeight="1" thickBot="1">
       <c r="B2" s="9">
         <v>1</v>
       </c>
@@ -1632,13 +1700,13 @@
         <v>0</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>105</v>
-      </c>
-      <c r="E2" s="10" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="3" spans="2:5" s="2" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E2" s="12" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="3" spans="2:5" s="2" customFormat="1" ht="20.25" customHeight="1" thickBot="1">
       <c r="B3" s="9">
         <v>2</v>
       </c>
@@ -1646,111 +1714,111 @@
         <v>0</v>
       </c>
       <c r="D3" s="10" t="s">
-        <v>106</v>
-      </c>
-      <c r="E3" s="10" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="4" spans="2:5" s="2" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E3" s="12" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="4" spans="2:5" s="2" customFormat="1" ht="20.25" customHeight="1" thickBot="1">
       <c r="B4" s="9">
         <v>3</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>184</v>
+        <v>86</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>107</v>
-      </c>
-      <c r="E4" s="10" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="5" spans="2:5" s="2" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E4" s="12" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="5" spans="2:5" s="2" customFormat="1" ht="20.25" customHeight="1" thickBot="1">
       <c r="B5" s="9">
         <v>4</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>175</v>
+        <v>77</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>108</v>
-      </c>
-      <c r="E5" s="10" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="6" spans="2:5" s="2" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E5" s="12" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="6" spans="2:5" s="2" customFormat="1" ht="20.25" customHeight="1" thickBot="1">
       <c r="B6" s="9">
         <v>5</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>176</v>
+        <v>78</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>109</v>
-      </c>
-      <c r="E6" s="10" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="7" spans="2:5" s="2" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E6" s="12" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="7" spans="2:5" s="2" customFormat="1" ht="20.25" customHeight="1" thickBot="1">
       <c r="B7" s="9">
         <v>6</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>185</v>
+        <v>87</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>110</v>
-      </c>
-      <c r="E7" s="10" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="8" spans="2:5" s="2" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E7" s="12" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="8" spans="2:5" s="2" customFormat="1" ht="20.25" customHeight="1" thickBot="1">
       <c r="B8" s="9">
         <v>7</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>185</v>
+        <v>87</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>111</v>
-      </c>
-      <c r="E8" s="10" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="9" spans="2:5" s="2" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E8" s="12" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="9" spans="2:5" s="2" customFormat="1" ht="20.25" customHeight="1" thickBot="1">
       <c r="B9" s="9">
         <v>8</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>186</v>
+        <v>88</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>112</v>
-      </c>
-      <c r="E9" s="10" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="10" spans="2:5" s="2" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E9" s="12" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="10" spans="2:5" s="2" customFormat="1" ht="20.25" customHeight="1" thickBot="1">
       <c r="B10" s="9">
         <v>9</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>187</v>
+        <v>89</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>113</v>
-      </c>
-      <c r="E10" s="10" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="11" spans="2:5" s="2" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E10" s="12" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="11" spans="2:5" s="2" customFormat="1" ht="20.25" customHeight="1" thickBot="1">
       <c r="B11" s="9">
         <v>10</v>
       </c>
@@ -1758,13 +1826,13 @@
         <v>1</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="E11" s="10" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="12" spans="2:5" s="2" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E11" s="12" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="12" spans="2:5" s="2" customFormat="1" ht="20.25" customHeight="1" thickBot="1">
       <c r="B12" s="9">
         <v>11</v>
       </c>
@@ -1772,853 +1840,853 @@
         <v>1</v>
       </c>
       <c r="D12" s="10" t="s">
-        <v>115</v>
-      </c>
-      <c r="E12" s="10" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="13" spans="2:5" s="2" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E12" s="12" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="13" spans="2:5" s="2" customFormat="1" ht="20.25" customHeight="1" thickBot="1">
       <c r="B13" s="9">
         <v>12</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>188</v>
+        <v>90</v>
       </c>
       <c r="D13" s="10" t="s">
-        <v>116</v>
-      </c>
-      <c r="E13" s="10" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="14" spans="2:5" s="2" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E13" s="12" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="14" spans="2:5" s="2" customFormat="1" ht="20.25" customHeight="1" thickBot="1">
       <c r="B14" s="9">
         <v>13</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>291</v>
+        <v>193</v>
       </c>
       <c r="D14" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="E14" s="10" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="15" spans="2:5" s="2" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E14" s="12" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="15" spans="2:5" s="2" customFormat="1" ht="20.25" customHeight="1" thickBot="1">
       <c r="B15" s="9">
         <v>14</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>292</v>
+        <v>194</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>118</v>
-      </c>
-      <c r="E15" s="10" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="16" spans="2:5" s="2" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E15" s="12" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="16" spans="2:5" s="2" customFormat="1" ht="20.25" customHeight="1" thickBot="1">
       <c r="B16" s="9">
         <v>15</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>293</v>
+        <v>195</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>119</v>
-      </c>
-      <c r="E16" s="10" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="17" spans="2:5" s="2" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E16" s="12" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="17" spans="2:5" s="2" customFormat="1" ht="20.25" customHeight="1" thickBot="1">
       <c r="B17" s="9">
         <v>16</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>294</v>
+        <v>196</v>
       </c>
       <c r="D17" s="10" t="s">
-        <v>120</v>
-      </c>
-      <c r="E17" s="10" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="18" spans="2:5" s="2" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E17" s="12" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="18" spans="2:5" s="2" customFormat="1" ht="20.25" customHeight="1" thickBot="1">
       <c r="B18" s="9">
         <v>17</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>294</v>
+        <v>196</v>
       </c>
       <c r="D18" s="10" t="s">
-        <v>121</v>
-      </c>
-      <c r="E18" s="10" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="19" spans="2:5" s="2" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E18" s="12" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="19" spans="2:5" s="2" customFormat="1" ht="20.25" customHeight="1" thickBot="1">
       <c r="B19" s="9">
         <v>18</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>294</v>
+        <v>196</v>
       </c>
       <c r="D19" s="10" t="s">
-        <v>122</v>
-      </c>
-      <c r="E19" s="10" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="20" spans="2:5" s="2" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E19" s="12" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="20" spans="2:5" s="2" customFormat="1" ht="20.25" customHeight="1" thickBot="1">
       <c r="B20" s="9">
         <v>19</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>183</v>
+        <v>85</v>
       </c>
       <c r="D20" s="10" t="s">
-        <v>123</v>
-      </c>
-      <c r="E20" s="10" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="21" spans="2:5" s="2" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E20" s="12" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="21" spans="2:5" s="2" customFormat="1" ht="20.25" customHeight="1" thickBot="1">
       <c r="B21" s="9">
         <v>20</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>295</v>
+        <v>197</v>
       </c>
       <c r="D21" s="10" t="s">
-        <v>124</v>
-      </c>
-      <c r="E21" s="10" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="22" spans="2:5" s="2" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E21" s="12" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="22" spans="2:5" s="2" customFormat="1" ht="20.25" customHeight="1" thickBot="1">
       <c r="B22" s="9">
         <v>21</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>177</v>
+        <v>79</v>
       </c>
       <c r="D22" s="10" t="s">
-        <v>125</v>
-      </c>
-      <c r="E22" s="10" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="23" spans="2:5" s="2" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E22" s="12" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="23" spans="2:5" s="2" customFormat="1" ht="20.25" customHeight="1" thickBot="1">
       <c r="B23" s="9">
         <v>22</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>296</v>
+        <v>198</v>
       </c>
       <c r="D23" s="10" t="s">
-        <v>126</v>
-      </c>
-      <c r="E23" s="10" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="24" spans="2:5" s="2" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E23" s="12" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="24" spans="2:5" s="2" customFormat="1" ht="20.25" customHeight="1" thickBot="1">
       <c r="B24" s="9">
         <v>23</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>178</v>
+        <v>80</v>
       </c>
       <c r="D24" s="10" t="s">
-        <v>127</v>
-      </c>
-      <c r="E24" s="10" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="25" spans="2:5" s="2" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E24" s="12" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="25" spans="2:5" s="2" customFormat="1" ht="20.25" customHeight="1" thickBot="1">
       <c r="B25" s="9">
         <v>24</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>297</v>
+        <v>199</v>
       </c>
       <c r="D25" s="10" t="s">
-        <v>128</v>
-      </c>
-      <c r="E25" s="10" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="26" spans="2:5" s="2" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E25" s="12" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="26" spans="2:5" s="2" customFormat="1" ht="20.25" customHeight="1" thickBot="1">
       <c r="B26" s="9">
         <v>25</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>298</v>
+        <v>200</v>
       </c>
       <c r="D26" s="10" t="s">
-        <v>129</v>
-      </c>
-      <c r="E26" s="10" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="27" spans="2:5" s="2" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E26" s="12" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="27" spans="2:5" s="2" customFormat="1" ht="20.25" customHeight="1" thickBot="1">
       <c r="B27" s="9">
         <v>26</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>298</v>
+        <v>200</v>
       </c>
       <c r="D27" s="10" t="s">
-        <v>130</v>
-      </c>
-      <c r="E27" s="10" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="28" spans="2:5" s="2" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E27" s="12" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="28" spans="2:5" s="2" customFormat="1" ht="20.25" customHeight="1" thickBot="1">
       <c r="B28" s="9">
         <v>27</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>179</v>
+        <v>81</v>
       </c>
       <c r="D28" s="10" t="s">
-        <v>131</v>
-      </c>
-      <c r="E28" s="10" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="29" spans="2:5" s="2" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E28" s="12" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="29" spans="2:5" s="2" customFormat="1" ht="20.25" customHeight="1" thickBot="1">
       <c r="B29" s="9">
         <v>28</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>180</v>
+        <v>82</v>
       </c>
       <c r="D29" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="E29" s="10" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="30" spans="2:5" s="2" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E29" s="12" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="30" spans="2:5" s="2" customFormat="1" ht="20.25" customHeight="1" thickBot="1">
       <c r="B30" s="9">
         <v>29</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>299</v>
+        <v>201</v>
       </c>
       <c r="D30" s="10" t="s">
-        <v>133</v>
-      </c>
-      <c r="E30" s="10" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="31" spans="2:5" s="2" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E30" s="12" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="31" spans="2:5" s="2" customFormat="1" ht="20.25" customHeight="1" thickBot="1">
       <c r="B31" s="9">
         <v>30</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>300</v>
+        <v>202</v>
       </c>
       <c r="D31" s="10" t="s">
-        <v>134</v>
-      </c>
-      <c r="E31" s="10" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="32" spans="2:5" s="2" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E31" s="12" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="32" spans="2:5" s="2" customFormat="1" ht="20.25" customHeight="1" thickBot="1">
       <c r="B32" s="9">
         <v>31</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>301</v>
+        <v>203</v>
       </c>
       <c r="D32" s="10" t="s">
-        <v>135</v>
-      </c>
-      <c r="E32" s="10" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="33" spans="2:5" s="2" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E32" s="12" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="33" spans="2:5" s="2" customFormat="1" ht="20.25" customHeight="1" thickBot="1">
       <c r="B33" s="9">
         <v>32</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>302</v>
+        <v>204</v>
       </c>
       <c r="D33" s="10" t="s">
-        <v>136</v>
-      </c>
-      <c r="E33" s="10" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="34" spans="2:5" s="2" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E33" s="12" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="34" spans="2:5" s="2" customFormat="1" ht="20.25" customHeight="1" thickBot="1">
       <c r="B34" s="9">
         <v>33</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>303</v>
+        <v>205</v>
       </c>
       <c r="D34" s="10" t="s">
-        <v>137</v>
-      </c>
-      <c r="E34" s="10" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="35" spans="2:5" s="2" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E34" s="12" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="35" spans="2:5" s="2" customFormat="1" ht="20.25" customHeight="1" thickBot="1">
       <c r="B35" s="9">
         <v>34</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>304</v>
+        <v>206</v>
       </c>
       <c r="D35" s="10" t="s">
-        <v>138</v>
-      </c>
-      <c r="E35" s="10" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="36" spans="2:5" s="2" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E35" s="12" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="36" spans="2:5" s="2" customFormat="1" ht="20.25" customHeight="1" thickBot="1">
       <c r="B36" s="9">
         <v>35</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>305</v>
+        <v>207</v>
       </c>
       <c r="D36" s="10" t="s">
-        <v>139</v>
-      </c>
-      <c r="E36" s="10" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="37" spans="2:5" s="2" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E36" s="12" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="37" spans="2:5" s="2" customFormat="1" ht="20.25" customHeight="1" thickBot="1">
       <c r="B37" s="9">
         <v>36</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>304</v>
+        <v>206</v>
       </c>
       <c r="D37" s="10" t="s">
-        <v>140</v>
-      </c>
-      <c r="E37" s="10" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="38" spans="2:5" s="2" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E37" s="12" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="38" spans="2:5" s="2" customFormat="1" ht="20.25" customHeight="1" thickBot="1">
       <c r="B38" s="9">
         <v>37</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>304</v>
+        <v>206</v>
       </c>
       <c r="D38" s="10" t="s">
-        <v>141</v>
-      </c>
-      <c r="E38" s="10" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="39" spans="2:5" s="2" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E38" s="12" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="39" spans="2:5" s="2" customFormat="1" ht="20.25" customHeight="1" thickBot="1">
       <c r="B39" s="9">
         <v>38</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>306</v>
+        <v>208</v>
       </c>
       <c r="D39" s="10" t="s">
-        <v>142</v>
-      </c>
-      <c r="E39" s="10" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="40" spans="2:5" s="2" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E39" s="12" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="40" spans="2:5" s="2" customFormat="1" ht="20.25" customHeight="1" thickBot="1">
       <c r="B40" s="9">
         <v>39</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>307</v>
+        <v>209</v>
       </c>
       <c r="D40" s="10" t="s">
-        <v>143</v>
-      </c>
-      <c r="E40" s="10" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="41" spans="2:5" s="2" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E40" s="12" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="41" spans="2:5" s="2" customFormat="1" ht="20.25" customHeight="1" thickBot="1">
       <c r="B41" s="9">
         <v>40</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>308</v>
+        <v>210</v>
       </c>
       <c r="D41" s="10" t="s">
-        <v>144</v>
-      </c>
-      <c r="E41" s="10" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="42" spans="2:5" s="2" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E41" s="12" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="42" spans="2:5" s="2" customFormat="1" ht="20.25" customHeight="1" thickBot="1">
       <c r="B42" s="9">
         <v>41</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>309</v>
+        <v>211</v>
       </c>
       <c r="D42" s="10" t="s">
-        <v>145</v>
-      </c>
-      <c r="E42" s="10" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="43" spans="2:5" s="2" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E42" s="12" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="43" spans="2:5" s="2" customFormat="1" ht="20.25" customHeight="1" thickBot="1">
       <c r="B43" s="9">
         <v>42</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>310</v>
+        <v>212</v>
       </c>
       <c r="D43" s="10" t="s">
-        <v>146</v>
-      </c>
-      <c r="E43" s="10" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="44" spans="2:5" s="2" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E43" s="12" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="44" spans="2:5" s="2" customFormat="1" ht="20.25" customHeight="1" thickBot="1">
       <c r="B44" s="9">
         <v>43</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>310</v>
+        <v>212</v>
       </c>
       <c r="D44" s="10" t="s">
-        <v>147</v>
-      </c>
-      <c r="E44" s="10" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="45" spans="2:5" s="2" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E44" s="12" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="45" spans="2:5" s="2" customFormat="1" ht="20.25" customHeight="1" thickBot="1">
       <c r="B45" s="9">
         <v>44</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>311</v>
+        <v>213</v>
       </c>
       <c r="D45" s="10" t="s">
-        <v>148</v>
-      </c>
-      <c r="E45" s="10" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="46" spans="2:5" s="2" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E45" s="12" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="46" spans="2:5" s="2" customFormat="1" ht="20.25" customHeight="1" thickBot="1">
       <c r="B46" s="9">
         <v>45</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>312</v>
+        <v>214</v>
       </c>
       <c r="D46" s="10" t="s">
-        <v>149</v>
-      </c>
-      <c r="E46" s="10" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="47" spans="2:5" s="2" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E46" s="12" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="47" spans="2:5" s="2" customFormat="1" ht="20.25" customHeight="1" thickBot="1">
       <c r="B47" s="9">
         <v>46</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>313</v>
+        <v>215</v>
       </c>
       <c r="D47" s="10" t="s">
-        <v>150</v>
-      </c>
-      <c r="E47" s="10" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="48" spans="2:5" s="2" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E47" s="12" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="48" spans="2:5" s="2" customFormat="1" ht="20.25" customHeight="1" thickBot="1">
       <c r="B48" s="9">
         <v>47</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>314</v>
+        <v>216</v>
       </c>
       <c r="D48" s="10" t="s">
-        <v>151</v>
-      </c>
-      <c r="E48" s="10" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="49" spans="2:5" s="2" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E48" s="12" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="49" spans="2:5" s="2" customFormat="1" ht="20.25" customHeight="1" thickBot="1">
       <c r="B49" s="9">
         <v>48</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>315</v>
+        <v>217</v>
       </c>
       <c r="D49" s="10" t="s">
-        <v>152</v>
-      </c>
-      <c r="E49" s="10" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="50" spans="2:5" s="2" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E49" s="12" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="50" spans="2:5" s="2" customFormat="1" ht="20.25" customHeight="1" thickBot="1">
       <c r="B50" s="9">
         <v>49</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>316</v>
+        <v>218</v>
       </c>
       <c r="D50" s="10" t="s">
-        <v>153</v>
-      </c>
-      <c r="E50" s="10" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="51" spans="2:5" s="2" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E50" s="12" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="51" spans="2:5" s="2" customFormat="1" ht="20.25" customHeight="1" thickBot="1">
       <c r="B51" s="9">
         <v>50</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>317</v>
+        <v>219</v>
       </c>
       <c r="D51" s="10" t="s">
-        <v>154</v>
-      </c>
-      <c r="E51" s="10" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="52" spans="2:5" s="2" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E51" s="12" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="52" spans="2:5" s="2" customFormat="1" ht="20.25" customHeight="1" thickBot="1">
       <c r="B52" s="9">
         <v>51</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>317</v>
+        <v>219</v>
       </c>
       <c r="D52" s="10" t="s">
-        <v>155</v>
-      </c>
-      <c r="E52" s="10" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="53" spans="2:5" s="2" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E52" s="12" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="53" spans="2:5" s="2" customFormat="1" ht="20.25" customHeight="1" thickBot="1">
       <c r="B53" s="9">
         <v>52</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>317</v>
+        <v>219</v>
       </c>
       <c r="D53" s="10" t="s">
-        <v>156</v>
-      </c>
-      <c r="E53" s="10" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="54" spans="2:5" s="2" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E53" s="12" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="54" spans="2:5" s="2" customFormat="1" ht="20.25" customHeight="1" thickBot="1">
       <c r="B54" s="9">
         <v>53</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>318</v>
+        <v>220</v>
       </c>
       <c r="D54" s="10" t="s">
-        <v>157</v>
-      </c>
-      <c r="E54" s="10" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="55" spans="2:5" s="2" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E54" s="12" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="55" spans="2:5" s="2" customFormat="1" ht="20.25" customHeight="1" thickBot="1">
       <c r="B55" s="9">
         <v>54</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>319</v>
+        <v>221</v>
       </c>
       <c r="D55" s="10" t="s">
-        <v>158</v>
-      </c>
-      <c r="E55" s="10" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="56" spans="2:5" s="2" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E55" s="12" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="56" spans="2:5" s="2" customFormat="1" ht="20.25" customHeight="1" thickBot="1">
       <c r="B56" s="9">
         <v>55</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>181</v>
+        <v>83</v>
       </c>
       <c r="D56" s="10" t="s">
-        <v>159</v>
-      </c>
-      <c r="E56" s="10" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="57" spans="2:5" s="2" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E56" s="12" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="57" spans="2:5" s="2" customFormat="1" ht="20.25" customHeight="1" thickBot="1">
       <c r="B57" s="9">
         <v>56</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>320</v>
+        <v>222</v>
       </c>
       <c r="D57" s="10" t="s">
-        <v>160</v>
-      </c>
-      <c r="E57" s="10" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="58" spans="2:5" s="2" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E57" s="12" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="58" spans="2:5" s="2" customFormat="1" ht="20.25" customHeight="1" thickBot="1">
       <c r="B58" s="9">
         <v>57</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>182</v>
+        <v>84</v>
       </c>
       <c r="D58" s="10" t="s">
-        <v>161</v>
-      </c>
-      <c r="E58" s="10" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="59" spans="2:5" s="2" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E58" s="12" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="59" spans="2:5" s="2" customFormat="1" ht="20.25" customHeight="1" thickBot="1">
       <c r="B59" s="9">
         <v>58</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>321</v>
+        <v>223</v>
       </c>
       <c r="D59" s="10" t="s">
-        <v>162</v>
-      </c>
-      <c r="E59" s="10" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="60" spans="2:5" s="2" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E59" s="12" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="60" spans="2:5" s="2" customFormat="1" ht="20.25" customHeight="1" thickBot="1">
       <c r="B60" s="9">
         <v>59</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>322</v>
+        <v>224</v>
       </c>
       <c r="D60" s="10" t="s">
-        <v>163</v>
-      </c>
-      <c r="E60" s="10" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="61" spans="2:5" s="2" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E60" s="12" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="61" spans="2:5" s="2" customFormat="1" ht="20.25" customHeight="1" thickBot="1">
       <c r="B61" s="9">
         <v>60</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>323</v>
+        <v>225</v>
       </c>
       <c r="D61" s="10" t="s">
-        <v>164</v>
-      </c>
-      <c r="E61" s="10" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="62" spans="2:5" s="2" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E61" s="12" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="62" spans="2:5" s="2" customFormat="1" ht="20.25" customHeight="1" thickBot="1">
       <c r="B62" s="9">
         <v>61</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>324</v>
+        <v>226</v>
       </c>
       <c r="D62" s="10" t="s">
-        <v>165</v>
-      </c>
-      <c r="E62" s="10" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="63" spans="2:5" s="2" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E62" s="12" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="63" spans="2:5" s="2" customFormat="1" ht="20.25" customHeight="1" thickBot="1">
       <c r="B63" s="9">
         <v>62</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>324</v>
+        <v>226</v>
       </c>
       <c r="D63" s="10" t="s">
-        <v>166</v>
-      </c>
-      <c r="E63" s="10" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="64" spans="2:5" s="2" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E63" s="12" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="64" spans="2:5" s="2" customFormat="1" ht="20.25" customHeight="1" thickBot="1">
       <c r="B64" s="9">
         <v>63</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>325</v>
+        <v>227</v>
       </c>
       <c r="D64" s="10" t="s">
-        <v>167</v>
-      </c>
-      <c r="E64" s="10" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="65" spans="2:5" s="2" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E64" s="12" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="65" spans="2:5" s="2" customFormat="1" ht="20.25" customHeight="1" thickBot="1">
       <c r="B65" s="9">
         <v>64</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>326</v>
+        <v>228</v>
       </c>
       <c r="D65" s="10" t="s">
-        <v>168</v>
-      </c>
-      <c r="E65" s="10" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="66" spans="2:5" s="2" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E65" s="12" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="66" spans="2:5" s="2" customFormat="1" ht="20.25" customHeight="1" thickBot="1">
       <c r="B66" s="9">
         <v>65</v>
       </c>
       <c r="C66" s="4" t="s">
-        <v>327</v>
+        <v>229</v>
       </c>
       <c r="D66" s="10" t="s">
-        <v>169</v>
-      </c>
-      <c r="E66" s="10" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="67" spans="2:5" s="2" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E66" s="12" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="67" spans="2:5" s="2" customFormat="1" ht="20.25" customHeight="1" thickBot="1">
       <c r="B67" s="9">
         <v>66</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>328</v>
+        <v>230</v>
       </c>
       <c r="D67" s="10" t="s">
-        <v>170</v>
-      </c>
-      <c r="E67" s="10" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="68" spans="2:5" s="2" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E67" s="12" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="68" spans="2:5" s="2" customFormat="1" ht="20.25" customHeight="1" thickBot="1">
       <c r="B68" s="9">
         <v>67</v>
       </c>
       <c r="C68" s="4" t="s">
-        <v>329</v>
+        <v>231</v>
       </c>
       <c r="D68" s="10" t="s">
-        <v>171</v>
-      </c>
-      <c r="E68" s="10" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="69" spans="2:5" s="2" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E68" s="12" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="69" spans="2:5" s="2" customFormat="1" ht="20.25" customHeight="1" thickBot="1">
       <c r="B69" s="9">
         <v>68</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>330</v>
+        <v>232</v>
       </c>
       <c r="D69" s="10" t="s">
-        <v>172</v>
-      </c>
-      <c r="E69" s="10" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="70" spans="2:5" s="2" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E69" s="12" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="70" spans="2:5" s="2" customFormat="1" ht="20.25" customHeight="1" thickBot="1">
       <c r="B70" s="9">
         <v>69</v>
       </c>
       <c r="C70" s="4" t="s">
-        <v>331</v>
+        <v>233</v>
       </c>
       <c r="D70" s="10" t="s">
-        <v>173</v>
-      </c>
-      <c r="E70" s="10" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="71" spans="2:5" s="2" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E70" s="12" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="71" spans="2:5" s="2" customFormat="1" ht="20.25" customHeight="1" thickBot="1">
       <c r="B71" s="9">
         <v>70</v>
       </c>
       <c r="C71" s="4" t="s">
-        <v>332</v>
+        <v>234</v>
       </c>
       <c r="D71" s="10" t="s">
-        <v>174</v>
-      </c>
-      <c r="E71" s="10" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="72" spans="2:5" s="2" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E71" s="12" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="72" spans="2:5" s="2" customFormat="1" ht="20.25" customHeight="1" thickBot="1">
       <c r="B72" s="9">
         <v>71</v>
       </c>
       <c r="C72" s="5" t="s">
-        <v>333</v>
+        <v>235</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="E72" s="10" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="73" spans="2:5" s="2" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>91</v>
+      </c>
+      <c r="E72" s="12" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="73" spans="2:5" s="2" customFormat="1" ht="20.25" customHeight="1" thickBot="1">
       <c r="B73" s="9">
         <v>72</v>
       </c>
@@ -2626,13 +2694,13 @@
         <v>0</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="E73" s="10" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="74" spans="2:5" s="2" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>92</v>
+      </c>
+      <c r="E73" s="12" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="74" spans="2:5" s="2" customFormat="1" ht="20.25" customHeight="1" thickBot="1">
       <c r="B74" s="9">
         <v>73</v>
       </c>
@@ -2640,640 +2708,640 @@
         <v>0</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="E74" s="10" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="75" spans="2:5" s="2" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>93</v>
+      </c>
+      <c r="E74" s="12" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="75" spans="2:5" s="2" customFormat="1" ht="20.25" customHeight="1" thickBot="1">
       <c r="B75" s="9">
         <v>74</v>
       </c>
       <c r="C75" s="5" t="s">
-        <v>334</v>
+        <v>236</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="E75" s="10" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="76" spans="2:5" s="2" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>94</v>
+      </c>
+      <c r="E75" s="12" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="76" spans="2:5" s="2" customFormat="1" ht="20.25" customHeight="1" thickBot="1">
       <c r="B76" s="9">
         <v>75</v>
       </c>
       <c r="C76" s="5" t="s">
-        <v>335</v>
+        <v>237</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="E76" s="10" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="77" spans="2:5" s="2" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>95</v>
+      </c>
+      <c r="E76" s="12" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="77" spans="2:5" s="2" customFormat="1" ht="20.25" customHeight="1" thickBot="1">
       <c r="B77" s="9">
         <v>76</v>
       </c>
       <c r="C77" s="5" t="s">
-        <v>336</v>
+        <v>238</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="E77" s="10" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="78" spans="2:5" s="2" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>96</v>
+      </c>
+      <c r="E77" s="12" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="78" spans="2:5" s="2" customFormat="1" ht="20.25" customHeight="1" thickBot="1">
       <c r="B78" s="9">
         <v>77</v>
       </c>
       <c r="C78" s="5" t="s">
-        <v>337</v>
+        <v>239</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="E78" s="10" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="79" spans="2:5" s="2" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>97</v>
+      </c>
+      <c r="E78" s="12" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="79" spans="2:5" s="2" customFormat="1" ht="20.25" customHeight="1" thickBot="1">
       <c r="B79" s="9">
         <v>78</v>
       </c>
       <c r="C79" s="5" t="s">
-        <v>338</v>
+        <v>240</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="E79" s="10" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="80" spans="2:5" s="2" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+      <c r="E79" s="12" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="80" spans="2:5" s="2" customFormat="1" ht="20.25" customHeight="1" thickBot="1">
       <c r="B80" s="9">
         <v>79</v>
       </c>
       <c r="C80" s="5" t="s">
-        <v>339</v>
+        <v>241</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="E80" s="10" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="81" spans="2:5" s="2" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>99</v>
+      </c>
+      <c r="E80" s="12" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="81" spans="2:5" s="2" customFormat="1" ht="20.25" customHeight="1" thickBot="1">
       <c r="B81" s="9">
         <v>80</v>
       </c>
       <c r="C81" s="5" t="s">
-        <v>340</v>
+        <v>242</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="E81" s="10" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="82" spans="2:5" s="2" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>100</v>
+      </c>
+      <c r="E81" s="12" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="82" spans="2:5" s="2" customFormat="1" ht="20.25" customHeight="1" thickBot="1">
       <c r="B82" s="9">
         <v>81</v>
       </c>
       <c r="C82" s="5" t="s">
-        <v>341</v>
+        <v>243</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="E82" s="10" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="83" spans="2:5" s="2" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>101</v>
+      </c>
+      <c r="E82" s="12" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="83" spans="2:5" s="2" customFormat="1" ht="20.25" customHeight="1" thickBot="1">
       <c r="B83" s="9">
         <v>82</v>
       </c>
       <c r="C83" s="5" t="s">
-        <v>342</v>
+        <v>244</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="E83" s="10" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="84" spans="2:5" s="2" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>102</v>
+      </c>
+      <c r="E83" s="12" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="84" spans="2:5" s="2" customFormat="1" ht="20.25" customHeight="1" thickBot="1">
       <c r="B84" s="9">
         <v>83</v>
       </c>
       <c r="C84" s="5" t="s">
-        <v>292</v>
+        <v>194</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="E84" s="10" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="85" spans="2:5" s="2" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>103</v>
+      </c>
+      <c r="E84" s="12" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="85" spans="2:5" s="2" customFormat="1" ht="20.25" customHeight="1" thickBot="1">
       <c r="B85" s="9">
         <v>84</v>
       </c>
       <c r="C85" s="5" t="s">
-        <v>292</v>
+        <v>194</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="E85" s="10" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="86" spans="2:5" s="2" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>104</v>
+      </c>
+      <c r="E85" s="12" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="86" spans="2:5" s="2" customFormat="1" ht="20.25" customHeight="1" thickBot="1">
       <c r="B86" s="9">
         <v>85</v>
       </c>
       <c r="C86" s="5" t="s">
-        <v>343</v>
+        <v>245</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="E86" s="10" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="87" spans="2:5" s="2" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>105</v>
+      </c>
+      <c r="E86" s="12" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="87" spans="2:5" s="2" customFormat="1" ht="20.25" customHeight="1" thickBot="1">
       <c r="B87" s="9">
         <v>86</v>
       </c>
       <c r="C87" s="5" t="s">
-        <v>344</v>
+        <v>246</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="E87" s="10" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="88" spans="2:5" s="2" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>106</v>
+      </c>
+      <c r="E87" s="12" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="88" spans="2:5" s="2" customFormat="1" ht="20.25" customHeight="1" thickBot="1">
       <c r="B88" s="9">
         <v>87</v>
       </c>
       <c r="C88" s="5" t="s">
-        <v>345</v>
+        <v>247</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="E88" s="10" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="89" spans="2:5" s="2" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>107</v>
+      </c>
+      <c r="E88" s="12" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="89" spans="2:5" s="2" customFormat="1" ht="20.25" customHeight="1" thickBot="1">
       <c r="B89" s="9">
         <v>88</v>
       </c>
       <c r="C89" s="5" t="s">
-        <v>346</v>
+        <v>248</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="E89" s="10" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="90" spans="2:5" s="2" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>108</v>
+      </c>
+      <c r="E89" s="12" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="90" spans="2:5" s="2" customFormat="1" ht="20.25" customHeight="1" thickBot="1">
       <c r="B90" s="9">
         <v>89</v>
       </c>
       <c r="C90" s="5" t="s">
-        <v>347</v>
+        <v>249</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="E90" s="10" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="91" spans="2:5" s="2" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+      <c r="E90" s="12" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="91" spans="2:5" s="2" customFormat="1" ht="20.25" customHeight="1" thickBot="1">
       <c r="B91" s="9">
         <v>90</v>
       </c>
       <c r="C91" s="5" t="s">
-        <v>348</v>
+        <v>250</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="E91" s="10" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="92" spans="2:5" s="2" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>110</v>
+      </c>
+      <c r="E91" s="12" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="92" spans="2:5" s="2" customFormat="1" ht="20.25" customHeight="1" thickBot="1">
       <c r="B92" s="9">
         <v>91</v>
       </c>
       <c r="C92" s="5" t="s">
-        <v>349</v>
+        <v>251</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="E92" s="10" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="93" spans="2:5" s="2" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>111</v>
+      </c>
+      <c r="E92" s="12" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="93" spans="2:5" s="2" customFormat="1" ht="20.25" customHeight="1" thickBot="1">
       <c r="B93" s="9">
         <v>92</v>
       </c>
       <c r="C93" s="5" t="s">
-        <v>237</v>
+        <v>139</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>210</v>
-      </c>
-      <c r="E93" s="10" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="94" spans="2:5" s="2" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>112</v>
+      </c>
+      <c r="E93" s="12" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="94" spans="2:5" s="2" customFormat="1" ht="20.25" customHeight="1" thickBot="1">
       <c r="B94" s="9">
         <v>93</v>
       </c>
       <c r="C94" s="5" t="s">
-        <v>332</v>
+        <v>234</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="E94" s="10" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="95" spans="2:5" s="2" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>113</v>
+      </c>
+      <c r="E94" s="12" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="95" spans="2:5" s="2" customFormat="1" ht="20.25" customHeight="1" thickBot="1">
       <c r="B95" s="9">
         <v>94</v>
       </c>
       <c r="C95" s="5" t="s">
-        <v>350</v>
+        <v>252</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="E95" s="10" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="96" spans="2:5" s="2" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>114</v>
+      </c>
+      <c r="E95" s="12" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="96" spans="2:5" s="2" customFormat="1" ht="20.25" customHeight="1" thickBot="1">
       <c r="B96" s="9">
         <v>95</v>
       </c>
       <c r="C96" s="5" t="s">
-        <v>351</v>
+        <v>253</v>
       </c>
       <c r="D96" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="E96" s="10" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="97" spans="2:5" s="2" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>115</v>
+      </c>
+      <c r="E96" s="12" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="97" spans="2:5" s="2" customFormat="1" ht="20.25" customHeight="1" thickBot="1">
       <c r="B97" s="9">
         <v>96</v>
       </c>
       <c r="C97" s="5" t="s">
-        <v>352</v>
+        <v>254</v>
       </c>
       <c r="D97" s="3" t="s">
-        <v>214</v>
-      </c>
-      <c r="E97" s="10" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="98" spans="2:5" s="2" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>116</v>
+      </c>
+      <c r="E97" s="12" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="98" spans="2:5" s="2" customFormat="1" ht="20.25" customHeight="1" thickBot="1">
       <c r="B98" s="9">
         <v>97</v>
       </c>
       <c r="C98" s="5" t="s">
-        <v>353</v>
+        <v>255</v>
       </c>
       <c r="D98" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="E98" s="10" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="99" spans="2:5" s="2" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>117</v>
+      </c>
+      <c r="E98" s="12" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="99" spans="2:5" s="2" customFormat="1" ht="20.25" customHeight="1" thickBot="1">
       <c r="B99" s="9">
         <v>98</v>
       </c>
       <c r="C99" s="5" t="s">
-        <v>354</v>
+        <v>256</v>
       </c>
       <c r="D99" s="3" t="s">
-        <v>216</v>
-      </c>
-      <c r="E99" s="10" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="100" spans="2:5" s="2" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>118</v>
+      </c>
+      <c r="E99" s="12" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="100" spans="2:5" s="2" customFormat="1" ht="20.25" customHeight="1" thickBot="1">
       <c r="B100" s="9">
         <v>99</v>
       </c>
       <c r="C100" s="5" t="s">
-        <v>313</v>
+        <v>215</v>
       </c>
       <c r="D100" s="3" t="s">
-        <v>217</v>
-      </c>
-      <c r="E100" s="10" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="101" spans="2:5" x14ac:dyDescent="0.25">
+        <v>119</v>
+      </c>
+      <c r="E100" s="12" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="101" spans="2:5" ht="30" thickBot="1">
       <c r="B101" s="9">
         <v>100</v>
       </c>
       <c r="C101" s="5" t="s">
-        <v>355</v>
+        <v>257</v>
       </c>
       <c r="D101" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="E101" s="10" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="102" spans="2:5" x14ac:dyDescent="0.25">
+        <v>120</v>
+      </c>
+      <c r="E101" s="12" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="102" spans="2:5" ht="30" thickBot="1">
       <c r="B102" s="9">
         <v>101</v>
       </c>
       <c r="C102" s="5" t="s">
-        <v>356</v>
+        <v>258</v>
       </c>
       <c r="D102" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="E102" s="10" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="103" spans="2:5" x14ac:dyDescent="0.25">
+        <v>121</v>
+      </c>
+      <c r="E102" s="12" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="103" spans="2:5" ht="30" thickBot="1">
       <c r="B103" s="9">
         <v>102</v>
       </c>
       <c r="C103" s="5" t="s">
-        <v>357</v>
+        <v>259</v>
       </c>
       <c r="D103" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="E103" s="10" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="104" spans="2:5" x14ac:dyDescent="0.25">
+        <v>122</v>
+      </c>
+      <c r="E103" s="12" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="104" spans="2:5" ht="30" thickBot="1">
       <c r="B104" s="9">
         <v>103</v>
       </c>
       <c r="C104" s="5" t="s">
-        <v>358</v>
+        <v>260</v>
       </c>
       <c r="D104" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="E104" s="10" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="105" spans="2:5" x14ac:dyDescent="0.25">
+        <v>123</v>
+      </c>
+      <c r="E104" s="12" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="105" spans="2:5" ht="30" thickBot="1">
       <c r="B105" s="9">
         <v>104</v>
       </c>
       <c r="C105" s="5" t="s">
-        <v>359</v>
+        <v>261</v>
       </c>
       <c r="D105" s="3" t="s">
-        <v>222</v>
-      </c>
-      <c r="E105" s="10" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="106" spans="2:5" x14ac:dyDescent="0.25">
+        <v>124</v>
+      </c>
+      <c r="E105" s="12" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="106" spans="2:5" ht="30" thickBot="1">
       <c r="B106" s="9">
         <v>105</v>
       </c>
       <c r="C106" s="5" t="s">
-        <v>360</v>
+        <v>262</v>
       </c>
       <c r="D106" s="3" t="s">
-        <v>223</v>
-      </c>
-      <c r="E106" s="10" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="107" spans="2:5" x14ac:dyDescent="0.25">
+        <v>125</v>
+      </c>
+      <c r="E106" s="12" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="107" spans="2:5" ht="30" thickBot="1">
       <c r="B107" s="9">
         <v>106</v>
       </c>
       <c r="C107" s="5" t="s">
-        <v>361</v>
+        <v>263</v>
       </c>
       <c r="D107" s="3" t="s">
-        <v>224</v>
-      </c>
-      <c r="E107" s="10" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="108" spans="2:5" x14ac:dyDescent="0.25">
+        <v>126</v>
+      </c>
+      <c r="E107" s="12" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="108" spans="2:5" ht="30" thickBot="1">
       <c r="B108" s="9">
         <v>107</v>
       </c>
       <c r="C108" s="5" t="s">
-        <v>362</v>
+        <v>264</v>
       </c>
       <c r="D108" s="3" t="s">
-        <v>225</v>
-      </c>
-      <c r="E108" s="10" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="109" spans="2:5" x14ac:dyDescent="0.25">
+        <v>127</v>
+      </c>
+      <c r="E108" s="12" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="109" spans="2:5" ht="30" thickBot="1">
       <c r="B109" s="9">
         <v>108</v>
       </c>
       <c r="C109" s="5" t="s">
-        <v>363</v>
+        <v>265</v>
       </c>
       <c r="D109" s="3" t="s">
-        <v>226</v>
-      </c>
-      <c r="E109" s="10" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="110" spans="2:5" x14ac:dyDescent="0.25">
+        <v>128</v>
+      </c>
+      <c r="E109" s="12" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="110" spans="2:5" ht="30" thickBot="1">
       <c r="B110" s="9">
         <v>109</v>
       </c>
       <c r="C110" s="5" t="s">
-        <v>294</v>
+        <v>196</v>
       </c>
       <c r="D110" s="3" t="s">
-        <v>227</v>
-      </c>
-      <c r="E110" s="10" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="111" spans="2:5" x14ac:dyDescent="0.25">
+        <v>129</v>
+      </c>
+      <c r="E110" s="12" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="111" spans="2:5" ht="30" thickBot="1">
       <c r="B111" s="9">
         <v>110</v>
       </c>
       <c r="C111" s="5" t="s">
-        <v>238</v>
+        <v>140</v>
       </c>
       <c r="D111" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="E111" s="10" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="112" spans="2:5" x14ac:dyDescent="0.25">
+        <v>130</v>
+      </c>
+      <c r="E111" s="12" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="112" spans="2:5" ht="30" thickBot="1">
       <c r="B112" s="9">
         <v>111</v>
       </c>
       <c r="C112" s="5" t="s">
-        <v>239</v>
+        <v>141</v>
       </c>
       <c r="D112" s="3" t="s">
-        <v>229</v>
-      </c>
-      <c r="E112" s="10" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="113" spans="2:5" x14ac:dyDescent="0.25">
+        <v>131</v>
+      </c>
+      <c r="E112" s="12" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="113" spans="2:5" ht="30" thickBot="1">
       <c r="B113" s="9">
         <v>112</v>
       </c>
       <c r="C113" s="5" t="s">
-        <v>364</v>
+        <v>266</v>
       </c>
       <c r="D113" s="3" t="s">
-        <v>230</v>
-      </c>
-      <c r="E113" s="10" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="114" spans="2:5" x14ac:dyDescent="0.25">
+        <v>132</v>
+      </c>
+      <c r="E113" s="12" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="114" spans="2:5" ht="30" thickBot="1">
       <c r="B114" s="9">
         <v>113</v>
       </c>
       <c r="C114" s="5" t="s">
-        <v>365</v>
+        <v>267</v>
       </c>
       <c r="D114" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="E114" s="10" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="115" spans="2:5" x14ac:dyDescent="0.25">
+        <v>133</v>
+      </c>
+      <c r="E114" s="12" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="115" spans="2:5" ht="30" thickBot="1">
       <c r="B115" s="9">
         <v>114</v>
       </c>
       <c r="C115" s="5" t="s">
-        <v>240</v>
+        <v>142</v>
       </c>
       <c r="D115" s="3" t="s">
-        <v>232</v>
-      </c>
-      <c r="E115" s="10" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="116" spans="2:5" x14ac:dyDescent="0.25">
+        <v>134</v>
+      </c>
+      <c r="E115" s="12" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="116" spans="2:5" ht="30" thickBot="1">
       <c r="B116" s="9">
         <v>115</v>
       </c>
       <c r="C116" s="5" t="s">
-        <v>366</v>
+        <v>268</v>
       </c>
       <c r="D116" s="3" t="s">
-        <v>233</v>
-      </c>
-      <c r="E116" s="10" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="117" spans="2:5" x14ac:dyDescent="0.25">
+        <v>135</v>
+      </c>
+      <c r="E116" s="12" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="117" spans="2:5" ht="30" thickBot="1">
       <c r="B117" s="9">
         <v>116</v>
       </c>
       <c r="C117" s="5" t="s">
-        <v>367</v>
+        <v>269</v>
       </c>
       <c r="D117" s="3" t="s">
-        <v>234</v>
-      </c>
-      <c r="E117" s="10" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="118" spans="2:5" x14ac:dyDescent="0.25">
+        <v>136</v>
+      </c>
+      <c r="E117" s="12" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="118" spans="2:5" ht="30" thickBot="1">
       <c r="B118" s="9">
         <v>117</v>
       </c>
       <c r="C118" s="5" t="s">
-        <v>368</v>
+        <v>270</v>
       </c>
       <c r="D118" s="3" t="s">
-        <v>235</v>
-      </c>
-      <c r="E118" s="10" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="119" spans="2:5" x14ac:dyDescent="0.25">
+        <v>137</v>
+      </c>
+      <c r="E118" s="12" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="119" spans="2:5" ht="30" thickBot="1">
       <c r="B119" s="9">
         <v>118</v>
       </c>
       <c r="C119" s="5" t="s">
-        <v>369</v>
+        <v>271</v>
       </c>
       <c r="D119" s="3" t="s">
-        <v>236</v>
-      </c>
-      <c r="E119" s="10" t="s">
-        <v>72</v>
+        <v>138</v>
+      </c>
+      <c r="E119" s="12" t="s">
+        <v>389</v>
       </c>
     </row>
   </sheetData>
@@ -3286,264 +3354,264 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86083AD1-B43D-403E-8003-83FDBA978241}">
   <dimension ref="A1:A51"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="147.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" ht="15.75" thickBot="1">
       <c r="A1" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" ht="15.75" thickBot="1">
       <c r="A2" s="11" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" ht="15.75" thickBot="1">
       <c r="A3" s="11" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" ht="15.75" thickBot="1">
       <c r="A4" s="11" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" ht="15.75" thickBot="1">
       <c r="A5" s="11" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" ht="15.75" thickBot="1">
       <c r="A6" s="11" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" ht="15.75" thickBot="1">
       <c r="A7" s="11" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" ht="15.75" thickBot="1">
       <c r="A8" s="11" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" ht="15.75" thickBot="1">
       <c r="A9" s="11" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" ht="15.75" thickBot="1">
       <c r="A10" s="11" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" ht="15.75" thickBot="1">
       <c r="A11" s="11" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" ht="15.75" thickBot="1">
       <c r="A12" s="11" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" ht="15.75" thickBot="1">
       <c r="A13" s="11" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" ht="15.75" thickBot="1">
       <c r="A14" s="11" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" ht="15.75" thickBot="1">
       <c r="A15" s="11" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" ht="15.75" thickBot="1">
       <c r="A16" s="11" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" ht="15.75" thickBot="1">
       <c r="A17" s="11" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" ht="15.75" thickBot="1">
       <c r="A18" s="11" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" ht="15.75" thickBot="1">
       <c r="A19" s="11" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" ht="15.75" thickBot="1">
       <c r="A20" s="11" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" ht="15.75" thickBot="1">
       <c r="A21" s="11" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" ht="15.75" thickBot="1">
       <c r="A22" s="11" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" ht="15.75" thickBot="1">
       <c r="A23" s="11" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" ht="15.75" thickBot="1">
       <c r="A24" s="11" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" ht="15.75" thickBot="1">
       <c r="A25" s="11" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" ht="15.75" thickBot="1">
       <c r="A26" s="11" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" ht="15.75" thickBot="1">
       <c r="A27" s="11" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" ht="15.75" thickBot="1">
       <c r="A28" s="11" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" ht="15.75" thickBot="1">
       <c r="A29" s="11" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="30" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" ht="15.75" thickBot="1">
       <c r="A30" s="11" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="31" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" ht="15.75" thickBot="1">
       <c r="A31" s="11" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="32" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" ht="15.75" thickBot="1">
       <c r="A32" s="11" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="33" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" ht="15.75" thickBot="1">
       <c r="A33" s="11" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="34" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" ht="15.75" thickBot="1">
       <c r="A34" s="11" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="35" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" ht="15.75" thickBot="1">
       <c r="A35" s="11" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="36" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" ht="15.75" thickBot="1">
       <c r="A36" s="11" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="37" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" ht="15.75" thickBot="1">
       <c r="A37" s="11" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="38" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" ht="15.75" thickBot="1">
       <c r="A38" s="11" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="39" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" ht="15.75" thickBot="1">
       <c r="A39" s="11" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="40" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" ht="15.75" thickBot="1">
       <c r="A40" s="11" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="41" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" ht="15.75" thickBot="1">
       <c r="A41" s="11" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="42" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1" ht="15.75" thickBot="1">
       <c r="A42" s="11" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="43" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" ht="15.75" thickBot="1">
       <c r="A43" s="11" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="44" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1" ht="15.75" thickBot="1">
       <c r="A44" s="11" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="45" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" ht="15.75" thickBot="1">
       <c r="A45" s="11" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="46" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1" ht="15.75" thickBot="1">
       <c r="A46" s="11" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="47" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1" ht="15.75" thickBot="1">
       <c r="A47" s="11" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="48" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1" ht="15.75" thickBot="1">
       <c r="A48" s="11" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="49" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" ht="15.75" thickBot="1">
       <c r="A49" s="11" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="50" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1" ht="15.75" thickBot="1">
       <c r="A50" s="11" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="51" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1" ht="15.75" thickBot="1">
       <c r="A51" s="11" t="s">
-        <v>290</v>
+        <v>192</v>
       </c>
     </row>
   </sheetData>
